--- a/Rekap_Pareto_LMO_5_Sheet.xlsx
+++ b/Rekap_Pareto_LMO_5_Sheet.xlsx
@@ -19,8 +19,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'LCI UT LMO'!$B$2:$I$82</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PROC UT LMO'!$B$2:$S$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PROC DOWN LMO'!$B$2:$S$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Audit Pareto'!$A$5:$J$259</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Audit Pareto'!$A$1:$J$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Audit Pareto'!$A$5:$J$261</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Audit Pareto'!$A$1:$J$261</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -3487,7 +3487,7 @@
       <c r="D76" s="45" t="inlineStr">
         <is>
           <t>4. Coal Barging
-Proses individual tidak tersedia pada PROC INTI LMO</t>
+Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E76" s="46" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P6" s="22" t="inlineStr">
         <is>
-          <t>Tidak ada pada sumber</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
@@ -4206,7 +4206,9 @@
         <v>0.00068895856</v>
       </c>
       <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
+      <c r="P12" s="2" t="n">
+        <v>0.027699688</v>
+      </c>
       <c r="Q12" s="2" t="n">
         <v>0.11674097</v>
       </c>
@@ -4240,7 +4242,9 @@
         <v>0.132173700578595</v>
       </c>
       <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+      <c r="P13" s="3" t="n">
+        <v>0.3016118646254013</v>
+      </c>
       <c r="Q13" s="3" t="n">
         <v>0.3097341026193566</v>
       </c>
@@ -4332,7 +4336,9 @@
         <v>0.0012837925</v>
       </c>
       <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
+      <c r="P16" s="2" t="n">
+        <v>0.051615081</v>
+      </c>
       <c r="Q16" s="2" t="n">
         <v>0.21753294</v>
       </c>
@@ -4368,7 +4374,9 @@
         <v>0.2462900025511634</v>
       </c>
       <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
+      <c r="P17" s="3" t="n">
+        <v>0.5620179123750826</v>
+      </c>
       <c r="Q17" s="3" t="n">
         <v>0.5771527336208561</v>
       </c>
@@ -4639,7 +4647,7 @@
     <row r="28" ht="27" customHeight="1">
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>Sumber: SimaPro LMO.xlsx / PROC INTI LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
+          <t>Sumber: SimaPro LMO.xlsx / PROC INTI LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di workbook gabungan / Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8201,7 @@
     <row r="28" ht="27" customHeight="1">
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>Sumber: SimaPro LMO.xlsx / PROC UT LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
+          <t>Sumber: SimaPro LMO.xlsx / PROC UT LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di workbook gabungan / Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8924,7 @@
     <row r="22" ht="27" customHeight="1">
       <c r="B22" s="49" t="inlineStr">
         <is>
-          <t>Sumber: SimaPro LMO.xlsx / PROC DWN LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
+          <t>Sumber: SimaPro LMO.xlsx / PROC DWN LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di workbook gabungan / Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J259"/>
+  <dimension ref="A1:J261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13847,7 +13855,7 @@
       </c>
       <c r="B113" s="60" t="inlineStr">
         <is>
-          <t>LUC</t>
+          <t>WSF</t>
         </is>
       </c>
       <c r="C113" s="61" t="inlineStr">
@@ -13862,22 +13870,22 @@
       </c>
       <c r="E113" s="61" t="inlineStr"/>
       <c r="F113" s="62" t="n">
-        <v>0.21753294</v>
+        <v>0.051615081</v>
       </c>
       <c r="G113" s="60" t="inlineStr">
         <is>
-          <t>m2a crop eq</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="H113" s="63" t="n">
-        <v>0.5771527336208561</v>
+        <v>0.5620179123750826</v>
       </c>
       <c r="I113" s="63" t="n">
-        <v>0.5771527336208561</v>
+        <v>0.5620179123750826</v>
       </c>
       <c r="J113" s="61" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>512</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13897,7 @@
       </c>
       <c r="B114" s="56" t="inlineStr">
         <is>
-          <t>LUC</t>
+          <t>WSF</t>
         </is>
       </c>
       <c r="C114" s="57" t="inlineStr">
@@ -13904,106 +13912,106 @@
       </c>
       <c r="E114" s="57" t="inlineStr"/>
       <c r="F114" s="58" t="n">
+        <v>0.027699688</v>
+      </c>
+      <c r="G114" s="56" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H114" s="59" t="n">
+        <v>0.3016118646254013</v>
+      </c>
+      <c r="I114" s="59" t="n">
+        <v>0.8636297770004839</v>
+      </c>
+      <c r="J114" s="57" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="60" t="inlineStr">
+        <is>
+          <t>PROC INTI LMO</t>
+        </is>
+      </c>
+      <c r="B115" s="60" t="inlineStr">
+        <is>
+          <t>LUC</t>
+        </is>
+      </c>
+      <c r="C115" s="61" t="inlineStr">
+        <is>
+          <t>2. Coal Hauling</t>
+        </is>
+      </c>
+      <c r="D115" s="61" t="inlineStr">
+        <is>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E115" s="61" t="inlineStr"/>
+      <c r="F115" s="62" t="n">
+        <v>0.21753294</v>
+      </c>
+      <c r="G115" s="60" t="inlineStr">
+        <is>
+          <t>m2a crop eq</t>
+        </is>
+      </c>
+      <c r="H115" s="63" t="n">
+        <v>0.5771527336208561</v>
+      </c>
+      <c r="I115" s="63" t="n">
+        <v>0.5771527336208561</v>
+      </c>
+      <c r="J115" s="61" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="56" t="inlineStr">
+        <is>
+          <t>PROC INTI LMO</t>
+        </is>
+      </c>
+      <c r="B116" s="56" t="inlineStr">
+        <is>
+          <t>LUC</t>
+        </is>
+      </c>
+      <c r="C116" s="57" t="inlineStr">
+        <is>
+          <t>1. Coal Mining</t>
+        </is>
+      </c>
+      <c r="D116" s="57" t="inlineStr">
+        <is>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E116" s="57" t="inlineStr"/>
+      <c r="F116" s="58" t="n">
         <v>0.11674097</v>
       </c>
-      <c r="G114" s="56" t="inlineStr">
+      <c r="G116" s="56" t="inlineStr">
         <is>
           <t>m2a crop eq</t>
         </is>
       </c>
-      <c r="H114" s="59" t="n">
+      <c r="H116" s="59" t="n">
         <v>0.3097341026193566</v>
       </c>
-      <c r="I114" s="59" t="n">
+      <c r="I116" s="59" t="n">
         <v>0.8868868362402127</v>
       </c>
-      <c r="J114" s="57" t="inlineStr">
+      <c r="J116" s="57" t="inlineStr">
         <is>
           <t>330</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="56" t="inlineStr">
-        <is>
-          <t>PROC INTI LMO</t>
-        </is>
-      </c>
-      <c r="B115" s="56" t="inlineStr">
-        <is>
-          <t>CEN</t>
-        </is>
-      </c>
-      <c r="C115" s="57" t="inlineStr">
-        <is>
-          <t>1. Coal Mining</t>
-        </is>
-      </c>
-      <c r="D115" s="57" t="inlineStr">
-        <is>
-          <t>1. Coal Mining</t>
-        </is>
-      </c>
-      <c r="E115" s="57" t="inlineStr"/>
-      <c r="F115" s="58" t="n">
-        <v>19100</v>
-      </c>
-      <c r="G115" s="56" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H115" s="59" t="n">
-        <v>0.9977482524018227</v>
-      </c>
-      <c r="I115" s="59" t="n">
-        <v>0.9977482524018227</v>
-      </c>
-      <c r="J115" s="57" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="64" t="inlineStr">
-        <is>
-          <t>PROC INTI LMO</t>
-        </is>
-      </c>
-      <c r="B116" s="64" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="C116" s="65" t="inlineStr">
-        <is>
-          <t>2. Coal Hauling</t>
-        </is>
-      </c>
-      <c r="D116" s="65" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E116" s="65" t="inlineStr"/>
-      <c r="F116" s="66" t="n">
-        <v>7.9899877804</v>
-      </c>
-      <c r="G116" s="64" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H116" s="67" t="n">
-        <v>0.636704820081451</v>
-      </c>
-      <c r="I116" s="67" t="n">
-        <v>0.636704820081451</v>
-      </c>
-      <c r="J116" s="65" t="inlineStr">
-        <is>
-          <t>434, 461, 487</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14023,7 @@
       </c>
       <c r="B117" s="56" t="inlineStr">
         <is>
-          <t>CED</t>
+          <t>CEN</t>
         </is>
       </c>
       <c r="C117" s="57" t="inlineStr">
@@ -14025,12 +14033,12 @@
       </c>
       <c r="D117" s="57" t="inlineStr">
         <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+          <t>1. Coal Mining</t>
         </is>
       </c>
       <c r="E117" s="57" t="inlineStr"/>
       <c r="F117" s="58" t="n">
-        <v>4.2878973044</v>
+        <v>19100</v>
       </c>
       <c r="G117" s="56" t="inlineStr">
         <is>
@@ -14038,106 +14046,98 @@
         </is>
       </c>
       <c r="H117" s="59" t="n">
-        <v>0.3416932486959403</v>
+        <v>0.9977482524018227</v>
       </c>
       <c r="I117" s="59" t="n">
-        <v>0.9783980687773913</v>
+        <v>0.9977482524018227</v>
       </c>
       <c r="J117" s="57" t="inlineStr">
         <is>
-          <t>434, 461, 487</t>
+          <t>356</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="64" t="inlineStr">
         <is>
-          <t>LCI UT LMO</t>
+          <t>PROC INTI LMO</t>
         </is>
       </c>
       <c r="B118" s="64" t="inlineStr">
         <is>
-          <t>GWP</t>
+          <t>CED</t>
         </is>
       </c>
       <c r="C118" s="65" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>2. Coal Hauling</t>
         </is>
       </c>
       <c r="D118" s="65" t="inlineStr">
         <is>
-          <t>Carbon dioxide, fossil</t>
-        </is>
-      </c>
-      <c r="E118" s="65" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E118" s="65" t="inlineStr"/>
       <c r="F118" s="66" t="n">
-        <v>0.33097784</v>
+        <v>7.9899877804</v>
       </c>
       <c r="G118" s="64" t="inlineStr">
         <is>
-          <t>kg CO2-eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H118" s="67" t="n">
-        <v>0.5027094970217253</v>
+        <v>0.636704820081451</v>
       </c>
       <c r="I118" s="67" t="n">
-        <v>0.5027094970217253</v>
+        <v>0.636704820081451</v>
       </c>
       <c r="J118" s="65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>434, 461, 487</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="56" t="inlineStr">
         <is>
-          <t>LCI UT LMO</t>
+          <t>PROC INTI LMO</t>
         </is>
       </c>
       <c r="B119" s="56" t="inlineStr">
         <is>
-          <t>GWP</t>
+          <t>CED</t>
         </is>
       </c>
       <c r="C119" s="57" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>1. Coal Mining</t>
         </is>
       </c>
       <c r="D119" s="57" t="inlineStr">
         <is>
-          <t>Carbon dioxide, fossil</t>
-        </is>
-      </c>
-      <c r="E119" s="57" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E119" s="57" t="inlineStr"/>
       <c r="F119" s="58" t="n">
-        <v>0.25642936</v>
+        <v>4.2878973044</v>
       </c>
       <c r="G119" s="56" t="inlineStr">
         <is>
-          <t>kg CO2-eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H119" s="59" t="n">
-        <v>0.3894806812057354</v>
+        <v>0.3416932486959403</v>
       </c>
       <c r="I119" s="59" t="n">
-        <v>0.8921901782274607</v>
+        <v>0.9783980687773913</v>
       </c>
       <c r="J119" s="57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>434, 461, 487</t>
         </is>
       </c>
     </row>
@@ -14149,17 +14149,17 @@
       </c>
       <c r="B120" s="64" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C120" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D120" s="65" t="inlineStr">
         <is>
-          <t>Methane, bromotrifluoro-, Halon 1301</t>
+          <t>Carbon dioxide, fossil</t>
         </is>
       </c>
       <c r="E120" s="65" t="inlineStr">
@@ -14168,22 +14168,22 @@
         </is>
       </c>
       <c r="F120" s="66" t="n">
-        <v>2.9307312e-08</v>
+        <v>0.33097784</v>
       </c>
       <c r="G120" s="64" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H120" s="67" t="n">
-        <v>0.7474936198973047</v>
+        <v>0.5027094970217253</v>
       </c>
       <c r="I120" s="67" t="n">
-        <v>0.7474936198973047</v>
+        <v>0.5027094970217253</v>
       </c>
       <c r="J120" s="65" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -14195,17 +14195,17 @@
       </c>
       <c r="B121" s="56" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C121" s="57" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D121" s="57" t="inlineStr">
         <is>
-          <t>Methane, bromotrifluoro-, Halon 1301</t>
+          <t>Carbon dioxide, fossil</t>
         </is>
       </c>
       <c r="E121" s="57" t="inlineStr">
@@ -14214,22 +14214,22 @@
         </is>
       </c>
       <c r="F121" s="58" t="n">
-        <v>3.2537793e-09</v>
+        <v>0.25642936</v>
       </c>
       <c r="G121" s="56" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H121" s="59" t="n">
-        <v>0.08298882092304877</v>
+        <v>0.3894806812057354</v>
       </c>
       <c r="I121" s="59" t="n">
-        <v>0.8304824408203535</v>
+        <v>0.8921901782274607</v>
       </c>
       <c r="J121" s="57" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -14241,17 +14241,17 @@
       </c>
       <c r="B122" s="64" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="C122" s="65" t="inlineStr">
         <is>
-          <t>3. Workshop</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D122" s="65" t="inlineStr">
         <is>
-          <t>Nitrogen oxides, ID</t>
+          <t>Methane, bromotrifluoro-, Halon 1301</t>
         </is>
       </c>
       <c r="E122" s="65" t="inlineStr">
@@ -14260,68 +14260,68 @@
         </is>
       </c>
       <c r="F122" s="66" t="n">
-        <v>0.0016691167</v>
+        <v>2.9307312e-08</v>
       </c>
       <c r="G122" s="64" t="inlineStr">
         <is>
-          <t>kg SO2 eq</t>
+          <t>kg CFC-11 eq</t>
         </is>
       </c>
       <c r="H122" s="67" t="n">
-        <v>0.4054080863615755</v>
+        <v>0.7474936198973047</v>
       </c>
       <c r="I122" s="67" t="n">
-        <v>0.4054080863615755</v>
+        <v>0.7474936198973047</v>
       </c>
       <c r="J122" s="65" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="60" t="inlineStr">
+      <c r="A123" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B123" s="60" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C123" s="61" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D123" s="61" t="inlineStr">
-        <is>
-          <t>Sulfur dioxide, ID</t>
-        </is>
-      </c>
-      <c r="E123" s="61" t="inlineStr">
+      <c r="B123" s="56" t="inlineStr">
+        <is>
+          <t>ODP</t>
+        </is>
+      </c>
+      <c r="C123" s="57" t="inlineStr">
+        <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D123" s="57" t="inlineStr">
+        <is>
+          <t>Methane, bromotrifluoro-, Halon 1301</t>
+        </is>
+      </c>
+      <c r="E123" s="57" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F123" s="62" t="n">
-        <v>0.00098677182</v>
-      </c>
-      <c r="G123" s="60" t="inlineStr">
-        <is>
-          <t>kg SO2 eq</t>
-        </is>
-      </c>
-      <c r="H123" s="63" t="n">
-        <v>0.2396748383271997</v>
-      </c>
-      <c r="I123" s="63" t="n">
-        <v>0.6450829246887752</v>
-      </c>
-      <c r="J123" s="61" t="inlineStr">
-        <is>
-          <t>106</t>
+      <c r="F123" s="58" t="n">
+        <v>3.2537793e-09</v>
+      </c>
+      <c r="G123" s="56" t="inlineStr">
+        <is>
+          <t>kg CFC-11 eq</t>
+        </is>
+      </c>
+      <c r="H123" s="59" t="n">
+        <v>0.08298882092304877</v>
+      </c>
+      <c r="I123" s="59" t="n">
+        <v>0.8304824408203535</v>
+      </c>
+      <c r="J123" s="57" t="inlineStr">
+        <is>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -14338,80 +14338,80 @@
       </c>
       <c r="C124" s="65" t="inlineStr">
         <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="D124" s="65" t="inlineStr">
+        <is>
+          <t>Nitrogen oxides, ID</t>
+        </is>
+      </c>
+      <c r="E124" s="65" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F124" s="66" t="n">
+        <v>0.0016691167</v>
+      </c>
+      <c r="G124" s="64" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H124" s="67" t="n">
+        <v>0.4054080863615755</v>
+      </c>
+      <c r="I124" s="67" t="n">
+        <v>0.4054080863615755</v>
+      </c>
+      <c r="J124" s="65" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="60" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B125" s="60" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C125" s="61" t="inlineStr">
+        <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D124" s="65" t="inlineStr">
-        <is>
-          <t>Nitrogen oxides, ID</t>
-        </is>
-      </c>
-      <c r="E124" s="65" t="inlineStr">
+      <c r="D125" s="61" t="inlineStr">
+        <is>
+          <t>Sulfur dioxide, ID</t>
+        </is>
+      </c>
+      <c r="E125" s="61" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F124" s="66" t="n">
-        <v>0.00034881689</v>
-      </c>
-      <c r="G124" s="64" t="inlineStr">
+      <c r="F125" s="62" t="n">
+        <v>0.00098677182</v>
+      </c>
+      <c r="G125" s="60" t="inlineStr">
         <is>
           <t>kg SO2 eq</t>
         </is>
       </c>
-      <c r="H124" s="67" t="n">
-        <v>0.08472336767434907</v>
-      </c>
-      <c r="I124" s="67" t="n">
-        <v>0.7298062923631242</v>
-      </c>
-      <c r="J124" s="65" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B125" s="56" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C125" s="57" t="inlineStr">
-        <is>
-          <t>3. Workshop</t>
-        </is>
-      </c>
-      <c r="D125" s="57" t="inlineStr">
-        <is>
-          <t>Sulfur dioxide, ID</t>
-        </is>
-      </c>
-      <c r="E125" s="57" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="F125" s="58" t="n">
-        <v>0.00031688736</v>
-      </c>
-      <c r="G125" s="56" t="inlineStr">
-        <is>
-          <t>kg SO2 eq</t>
-        </is>
-      </c>
-      <c r="H125" s="59" t="n">
-        <v>0.07696807431725515</v>
-      </c>
-      <c r="I125" s="59" t="n">
-        <v>0.8067743666803794</v>
-      </c>
-      <c r="J125" s="57" t="inlineStr">
+      <c r="H125" s="63" t="n">
+        <v>0.2396748383271997</v>
+      </c>
+      <c r="I125" s="63" t="n">
+        <v>0.6450829246887752</v>
+      </c>
+      <c r="J125" s="61" t="inlineStr">
         <is>
           <t>106</t>
         </is>
@@ -14425,131 +14425,131 @@
       </c>
       <c r="B126" s="64" t="inlineStr">
         <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C126" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D126" s="65" t="inlineStr">
+        <is>
+          <t>Nitrogen oxides, ID</t>
+        </is>
+      </c>
+      <c r="E126" s="65" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F126" s="66" t="n">
+        <v>0.00034881689</v>
+      </c>
+      <c r="G126" s="64" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H126" s="67" t="n">
+        <v>0.08472336767434907</v>
+      </c>
+      <c r="I126" s="67" t="n">
+        <v>0.7298062923631242</v>
+      </c>
+      <c r="J126" s="65" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="56" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B127" s="56" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C127" s="57" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="D127" s="57" t="inlineStr">
+        <is>
+          <t>Sulfur dioxide, ID</t>
+        </is>
+      </c>
+      <c r="E127" s="57" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F127" s="58" t="n">
+        <v>0.00031688736</v>
+      </c>
+      <c r="G127" s="56" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H127" s="59" t="n">
+        <v>0.07696807431725515</v>
+      </c>
+      <c r="I127" s="59" t="n">
+        <v>0.8067743666803794</v>
+      </c>
+      <c r="J127" s="57" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="64" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B128" s="64" t="inlineStr">
+        <is>
           <t>EP</t>
         </is>
       </c>
-      <c r="C126" s="65" t="inlineStr">
+      <c r="C128" s="65" t="inlineStr">
         <is>
           <t>3. Workshop</t>
         </is>
       </c>
-      <c r="D126" s="65" t="inlineStr">
+      <c r="D128" s="65" t="inlineStr">
         <is>
           <t>Nitrogen oxides, ID</t>
         </is>
       </c>
-      <c r="E126" s="65" t="inlineStr">
+      <c r="E128" s="65" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F126" s="66" t="n">
+      <c r="F128" s="66" t="n">
         <v>0.00043397033</v>
       </c>
-      <c r="G126" s="64" t="inlineStr">
+      <c r="G128" s="64" t="inlineStr">
         <is>
           <t>kg PO4--- eq</t>
         </is>
       </c>
-      <c r="H126" s="67" t="n">
+      <c r="H128" s="67" t="n">
         <v>0.4623660459823359</v>
       </c>
-      <c r="I126" s="67" t="n">
+      <c r="I128" s="67" t="n">
         <v>0.4623660459823359</v>
       </c>
-      <c r="J126" s="65" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="60" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B127" s="60" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C127" s="61" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D127" s="61" t="inlineStr">
-        <is>
-          <t>Nitrate</t>
-        </is>
-      </c>
-      <c r="E127" s="61" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F127" s="62" t="n">
-        <v>0.00024708801</v>
-      </c>
-      <c r="G127" s="60" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H127" s="63" t="n">
-        <v>0.2632555690923476</v>
-      </c>
-      <c r="I127" s="63" t="n">
-        <v>0.7256216150746835</v>
-      </c>
-      <c r="J127" s="61" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="30" customHeight="1">
-      <c r="A128" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B128" s="56" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C128" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D128" s="57" t="inlineStr">
-        <is>
-          <t>Nitrogen oxides, ID</t>
-        </is>
-      </c>
-      <c r="E128" s="57" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="F128" s="58" t="n">
-        <v>9.0692391e-05</v>
-      </c>
-      <c r="G128" s="56" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H128" s="59" t="n">
-        <v>0.09662661091912435</v>
-      </c>
-      <c r="I128" s="59" t="n">
-        <v>0.8222482259938079</v>
-      </c>
-      <c r="J128" s="57" t="inlineStr">
+      <c r="J128" s="65" t="inlineStr">
         <is>
           <t>132</t>
         </is>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="B129" s="60" t="inlineStr">
         <is>
-          <t>POFP</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C129" s="61" t="inlineStr">
@@ -14573,77 +14573,77 @@
       </c>
       <c r="D129" s="61" t="inlineStr">
         <is>
-          <t>Carbon monoxide, fossil</t>
+          <t>Nitrate</t>
         </is>
       </c>
       <c r="E129" s="61" t="inlineStr">
         <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F129" s="62" t="n">
+        <v>0.00024708801</v>
+      </c>
+      <c r="G129" s="60" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H129" s="63" t="n">
+        <v>0.2632555690923476</v>
+      </c>
+      <c r="I129" s="63" t="n">
+        <v>0.7256216150746835</v>
+      </c>
+      <c r="J129" s="61" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="56" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B130" s="56" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C130" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D130" s="57" t="inlineStr">
+        <is>
+          <t>Nitrogen oxides, ID</t>
+        </is>
+      </c>
+      <c r="E130" s="57" t="inlineStr">
+        <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F129" s="62" t="n">
-        <v>6.338363899999999e-05</v>
-      </c>
-      <c r="G129" s="60" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H129" s="63" t="n">
-        <v>0.2929295226521161</v>
-      </c>
-      <c r="I129" s="63" t="n">
-        <v>0.2929295226521161</v>
-      </c>
-      <c r="J129" s="61" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="30" customHeight="1">
-      <c r="A130" s="64" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B130" s="64" t="inlineStr">
-        <is>
-          <t>POFP</t>
-        </is>
-      </c>
-      <c r="C130" s="65" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D130" s="65" t="inlineStr">
-        <is>
-          <t>Sulfur dioxide, ID</t>
-        </is>
-      </c>
-      <c r="E130" s="65" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="F130" s="66" t="n">
-        <v>3.9470873e-05</v>
-      </c>
-      <c r="G130" s="64" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H130" s="67" t="n">
-        <v>0.1824159068328705</v>
-      </c>
-      <c r="I130" s="67" t="n">
-        <v>0.4753454294849866</v>
-      </c>
-      <c r="J130" s="65" t="inlineStr">
-        <is>
-          <t>172</t>
+      <c r="F130" s="58" t="n">
+        <v>9.0692391e-05</v>
+      </c>
+      <c r="G130" s="56" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H130" s="59" t="n">
+        <v>0.09662661091912435</v>
+      </c>
+      <c r="I130" s="59" t="n">
+        <v>0.8222482259938079</v>
+      </c>
+      <c r="J130" s="57" t="inlineStr">
+        <is>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="D131" s="61" t="inlineStr">
         <is>
-          <t>Hexane</t>
+          <t>Carbon monoxide, fossil</t>
         </is>
       </c>
       <c r="E131" s="61" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="F131" s="62" t="n">
-        <v>3.4601452e-05</v>
+        <v>6.338363899999999e-05</v>
       </c>
       <c r="G131" s="60" t="inlineStr">
         <is>
@@ -14682,14 +14682,14 @@
         </is>
       </c>
       <c r="H131" s="63" t="n">
-        <v>0.1599117213423184</v>
+        <v>0.2929295226521161</v>
       </c>
       <c r="I131" s="63" t="n">
-        <v>0.6352571508273051</v>
+        <v>0.2929295226521161</v>
       </c>
       <c r="J131" s="61" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="C132" s="65" t="inlineStr">
         <is>
-          <t>3. Workshop</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D132" s="65" t="inlineStr">
@@ -14720,7 +14720,7 @@
         </is>
       </c>
       <c r="F132" s="66" t="n">
-        <v>1.2675494e-05</v>
+        <v>3.9470873e-05</v>
       </c>
       <c r="G132" s="64" t="inlineStr">
         <is>
@@ -14728,10 +14728,10 @@
         </is>
       </c>
       <c r="H132" s="67" t="n">
-        <v>0.05858020248411047</v>
+        <v>0.1824159068328705</v>
       </c>
       <c r="I132" s="67" t="n">
-        <v>0.6938373533114155</v>
+        <v>0.4753454294849866</v>
       </c>
       <c r="J132" s="65" t="inlineStr">
         <is>
@@ -14752,12 +14752,12 @@
       </c>
       <c r="C133" s="61" t="inlineStr">
         <is>
-          <t>3. Workshop</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D133" s="61" t="inlineStr">
         <is>
-          <t>Carbon monoxide</t>
+          <t>Hexane</t>
         </is>
       </c>
       <c r="E133" s="61" t="inlineStr">
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="F133" s="62" t="n">
-        <v>9.622202699999999e-06</v>
+        <v>3.4601452e-05</v>
       </c>
       <c r="G133" s="60" t="inlineStr">
         <is>
@@ -14774,14 +14774,14 @@
         </is>
       </c>
       <c r="H133" s="63" t="n">
-        <v>0.04446931871129871</v>
+        <v>0.1599117213423184</v>
       </c>
       <c r="I133" s="63" t="n">
-        <v>0.7383066720227142</v>
+        <v>0.6352571508273051</v>
       </c>
       <c r="J133" s="61" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -14798,12 +14798,12 @@
       </c>
       <c r="C134" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>3. Workshop</t>
         </is>
       </c>
       <c r="D134" s="65" t="inlineStr">
         <is>
-          <t>Sulfur dioxide</t>
+          <t>Sulfur dioxide, ID</t>
         </is>
       </c>
       <c r="E134" s="65" t="inlineStr">
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="F134" s="66" t="n">
-        <v>8.2625844e-06</v>
+        <v>1.2675494e-05</v>
       </c>
       <c r="G134" s="64" t="inlineStr">
         <is>
@@ -14820,60 +14820,60 @@
         </is>
       </c>
       <c r="H134" s="67" t="n">
-        <v>0.03818579908554669</v>
+        <v>0.05858020248411047</v>
       </c>
       <c r="I134" s="67" t="n">
-        <v>0.7764924711082608</v>
+        <v>0.6938373533114155</v>
       </c>
       <c r="J134" s="65" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>172</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="56" t="inlineStr">
+      <c r="A135" s="60" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B135" s="56" t="inlineStr">
+      <c r="B135" s="60" t="inlineStr">
         <is>
           <t>POFP</t>
         </is>
       </c>
-      <c r="C135" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D135" s="57" t="inlineStr">
-        <is>
-          <t>Ethene</t>
-        </is>
-      </c>
-      <c r="E135" s="57" t="inlineStr">
+      <c r="C135" s="61" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="D135" s="61" t="inlineStr">
+        <is>
+          <t>Carbon monoxide</t>
+        </is>
+      </c>
+      <c r="E135" s="61" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F135" s="58" t="n">
-        <v>7.2816847e-06</v>
-      </c>
-      <c r="G135" s="56" t="inlineStr">
+      <c r="F135" s="62" t="n">
+        <v>9.622202699999999e-06</v>
+      </c>
+      <c r="G135" s="60" t="inlineStr">
         <is>
           <t>kg C2H4 eq</t>
         </is>
       </c>
-      <c r="H135" s="59" t="n">
-        <v>0.03365253962894458</v>
-      </c>
-      <c r="I135" s="59" t="n">
-        <v>0.8101450107372054</v>
-      </c>
-      <c r="J135" s="57" t="inlineStr">
-        <is>
-          <t>176</t>
+      <c r="H135" s="63" t="n">
+        <v>0.04446931871129871</v>
+      </c>
+      <c r="I135" s="63" t="n">
+        <v>0.7383066720227142</v>
+      </c>
+      <c r="J135" s="61" t="inlineStr">
+        <is>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -14885,131 +14885,131 @@
       </c>
       <c r="B136" s="64" t="inlineStr">
         <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="C136" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D136" s="65" t="inlineStr">
+        <is>
+          <t>Sulfur dioxide</t>
+        </is>
+      </c>
+      <c r="E136" s="65" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F136" s="66" t="n">
+        <v>8.2625844e-06</v>
+      </c>
+      <c r="G136" s="64" t="inlineStr">
+        <is>
+          <t>kg C2H4 eq</t>
+        </is>
+      </c>
+      <c r="H136" s="67" t="n">
+        <v>0.03818579908554669</v>
+      </c>
+      <c r="I136" s="67" t="n">
+        <v>0.7764924711082608</v>
+      </c>
+      <c r="J136" s="65" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="56" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B137" s="56" t="inlineStr">
+        <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="C137" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D137" s="57" t="inlineStr">
+        <is>
+          <t>Ethene</t>
+        </is>
+      </c>
+      <c r="E137" s="57" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F137" s="58" t="n">
+        <v>7.2816847e-06</v>
+      </c>
+      <c r="G137" s="56" t="inlineStr">
+        <is>
+          <t>kg C2H4 eq</t>
+        </is>
+      </c>
+      <c r="H137" s="59" t="n">
+        <v>0.03365253962894458</v>
+      </c>
+      <c r="I137" s="59" t="n">
+        <v>0.8101450107372054</v>
+      </c>
+      <c r="J137" s="57" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="64" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B138" s="64" t="inlineStr">
+        <is>
           <t>ABF</t>
         </is>
       </c>
-      <c r="C136" s="65" t="inlineStr">
+      <c r="C138" s="65" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D136" s="65" t="inlineStr">
+      <c r="D138" s="65" t="inlineStr">
         <is>
           <t>Oil, crude</t>
         </is>
       </c>
-      <c r="E136" s="65" t="inlineStr">
+      <c r="E138" s="65" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F136" s="66" t="n">
+      <c r="F138" s="66" t="n">
         <v>2.1215233</v>
       </c>
-      <c r="G136" s="64" t="inlineStr">
+      <c r="G138" s="64" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H136" s="67" t="n">
+      <c r="H138" s="67" t="n">
         <v>0.6848350898738131</v>
       </c>
-      <c r="I136" s="67" t="n">
+      <c r="I138" s="67" t="n">
         <v>0.6848350898738131</v>
       </c>
-      <c r="J136" s="65" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="60" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B137" s="60" t="inlineStr">
-        <is>
-          <t>ABF</t>
-        </is>
-      </c>
-      <c r="C137" s="61" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D137" s="61" t="inlineStr">
-        <is>
-          <t>Oil, crude</t>
-        </is>
-      </c>
-      <c r="E137" s="61" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F137" s="62" t="n">
-        <v>0.24465283</v>
-      </c>
-      <c r="G137" s="60" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H137" s="63" t="n">
-        <v>0.07897478327055504</v>
-      </c>
-      <c r="I137" s="63" t="n">
-        <v>0.7638098731443682</v>
-      </c>
-      <c r="J137" s="61" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="30" customHeight="1">
-      <c r="A138" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B138" s="56" t="inlineStr">
-        <is>
-          <t>ABF</t>
-        </is>
-      </c>
-      <c r="C138" s="57" t="inlineStr">
-        <is>
-          <t>2. Wastewater Treatment Plant</t>
-        </is>
-      </c>
-      <c r="D138" s="57" t="inlineStr">
-        <is>
-          <t>Oil, crude</t>
-        </is>
-      </c>
-      <c r="E138" s="57" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F138" s="58" t="n">
-        <v>0.18003669</v>
-      </c>
-      <c r="G138" s="56" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H138" s="59" t="n">
-        <v>0.0581164688489322</v>
-      </c>
-      <c r="I138" s="59" t="n">
-        <v>0.8219263419933004</v>
-      </c>
-      <c r="J138" s="57" t="inlineStr">
+      <c r="J138" s="65" t="inlineStr">
         <is>
           <t>310</t>
         </is>
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B139" s="60" t="inlineStr">
         <is>
-          <t>ABN</t>
+          <t>ABF</t>
         </is>
       </c>
       <c r="C139" s="61" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D139" s="61" t="inlineStr">
         <is>
-          <t>Tellurium</t>
+          <t>Oil, crude</t>
         </is>
       </c>
       <c r="E139" s="61" t="inlineStr">
@@ -15042,68 +15042,68 @@
         </is>
       </c>
       <c r="F139" s="62" t="n">
-        <v>1.0060336e-07</v>
+        <v>0.24465283</v>
       </c>
       <c r="G139" s="60" t="inlineStr">
         <is>
-          <t>kg Sb eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H139" s="63" t="n">
-        <v>0.2407418468293587</v>
+        <v>0.07897478327055504</v>
       </c>
       <c r="I139" s="63" t="n">
-        <v>0.2407418468293587</v>
+        <v>0.7638098731443682</v>
       </c>
       <c r="J139" s="61" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>310</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="64" t="inlineStr">
+      <c r="A140" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B140" s="64" t="inlineStr">
-        <is>
-          <t>ABN</t>
-        </is>
-      </c>
-      <c r="C140" s="65" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D140" s="65" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E140" s="65" t="inlineStr">
+      <c r="B140" s="56" t="inlineStr">
+        <is>
+          <t>ABF</t>
+        </is>
+      </c>
+      <c r="C140" s="57" t="inlineStr">
+        <is>
+          <t>2. Wastewater Treatment Plant</t>
+        </is>
+      </c>
+      <c r="D140" s="57" t="inlineStr">
+        <is>
+          <t>Oil, crude</t>
+        </is>
+      </c>
+      <c r="E140" s="57" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F140" s="66" t="n">
-        <v>6.4870189e-08</v>
-      </c>
-      <c r="G140" s="64" t="inlineStr">
-        <is>
-          <t>kg Sb eq</t>
-        </is>
-      </c>
-      <c r="H140" s="67" t="n">
-        <v>0.1552330767484262</v>
-      </c>
-      <c r="I140" s="67" t="n">
-        <v>0.3959749235777849</v>
-      </c>
-      <c r="J140" s="65" t="inlineStr">
-        <is>
-          <t>251</t>
+      <c r="F140" s="58" t="n">
+        <v>0.18003669</v>
+      </c>
+      <c r="G140" s="56" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H140" s="59" t="n">
+        <v>0.0581164688489322</v>
+      </c>
+      <c r="I140" s="59" t="n">
+        <v>0.8219263419933004</v>
+      </c>
+      <c r="J140" s="57" t="inlineStr">
+        <is>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
       </c>
       <c r="D141" s="61" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tellurium</t>
         </is>
       </c>
       <c r="E141" s="61" t="inlineStr">
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="F141" s="62" t="n">
-        <v>3.2936577e-08</v>
+        <v>1.0060336e-07</v>
       </c>
       <c r="G141" s="60" t="inlineStr">
         <is>
@@ -15142,14 +15142,14 @@
         </is>
       </c>
       <c r="H141" s="63" t="n">
-        <v>0.07881657605886502</v>
+        <v>0.2407418468293587</v>
       </c>
       <c r="I141" s="63" t="n">
-        <v>0.4747914996366499</v>
+        <v>0.2407418468293587</v>
       </c>
       <c r="J141" s="61" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -15166,12 +15166,12 @@
       </c>
       <c r="C142" s="65" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D142" s="65" t="inlineStr">
         <is>
-          <t>Tellurium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="E142" s="65" t="inlineStr">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="F142" s="66" t="n">
-        <v>2.9526098e-08</v>
+        <v>6.4870189e-08</v>
       </c>
       <c r="G142" s="64" t="inlineStr">
         <is>
@@ -15188,14 +15188,14 @@
         </is>
       </c>
       <c r="H142" s="67" t="n">
-        <v>0.07065536739711908</v>
+        <v>0.1552330767484262</v>
       </c>
       <c r="I142" s="67" t="n">
-        <v>0.545446867033769</v>
+        <v>0.3959749235777849</v>
       </c>
       <c r="J142" s="65" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>251</t>
         </is>
       </c>
     </row>
@@ -15217,7 +15217,7 @@
       </c>
       <c r="D143" s="61" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E143" s="61" t="inlineStr">
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="F143" s="62" t="n">
-        <v>2.5511851e-08</v>
+        <v>3.2936577e-08</v>
       </c>
       <c r="G143" s="60" t="inlineStr">
         <is>
@@ -15234,14 +15234,14 @@
         </is>
       </c>
       <c r="H143" s="63" t="n">
-        <v>0.06104935387620673</v>
+        <v>0.07881657605886502</v>
       </c>
       <c r="I143" s="63" t="n">
-        <v>0.6064962209099757</v>
+        <v>0.4747914996366499</v>
       </c>
       <c r="J143" s="61" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>252</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C144" s="65" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D144" s="65" t="inlineStr">
@@ -15272,7 +15272,7 @@
         </is>
       </c>
       <c r="F144" s="66" t="n">
-        <v>1.9593178e-08</v>
+        <v>2.9526098e-08</v>
       </c>
       <c r="G144" s="64" t="inlineStr">
         <is>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="H144" s="67" t="n">
-        <v>0.04688608667718813</v>
+        <v>0.07065536739711908</v>
       </c>
       <c r="I144" s="67" t="n">
-        <v>0.6533823075871638</v>
+        <v>0.545446867033769</v>
       </c>
       <c r="J144" s="65" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D145" s="61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="E145" s="61" t="inlineStr">
@@ -15318,7 +15318,7 @@
         </is>
       </c>
       <c r="F145" s="62" t="n">
-        <v>1.8599925e-08</v>
+        <v>2.5511851e-08</v>
       </c>
       <c r="G145" s="60" t="inlineStr">
         <is>
@@ -15326,14 +15326,14 @@
         </is>
       </c>
       <c r="H145" s="63" t="n">
-        <v>0.04450925193142217</v>
+        <v>0.06104935387620673</v>
       </c>
       <c r="I145" s="63" t="n">
-        <v>0.6978915595185859</v>
+        <v>0.6064962209099757</v>
       </c>
       <c r="J145" s="61" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>254</t>
         </is>
       </c>
     </row>
@@ -15350,12 +15350,12 @@
       </c>
       <c r="C146" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D146" s="65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tellurium</t>
         </is>
       </c>
       <c r="E146" s="65" t="inlineStr">
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="F146" s="66" t="n">
-        <v>1.3287506e-08</v>
+        <v>1.9593178e-08</v>
       </c>
       <c r="G146" s="64" t="inlineStr">
         <is>
@@ -15372,14 +15372,14 @@
         </is>
       </c>
       <c r="H146" s="67" t="n">
-        <v>0.03179673854030506</v>
+        <v>0.04688608667718813</v>
       </c>
       <c r="I146" s="67" t="n">
-        <v>0.729688298058891</v>
+        <v>0.6533823075871638</v>
       </c>
       <c r="J146" s="65" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="C147" s="61" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D147" s="61" t="inlineStr">
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="F147" s="62" t="n">
-        <v>1.1230718e-08</v>
+        <v>1.8599925e-08</v>
       </c>
       <c r="G147" s="60" t="inlineStr">
         <is>
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="H147" s="63" t="n">
-        <v>0.02687488561554725</v>
+        <v>0.04450925193142217</v>
       </c>
       <c r="I147" s="63" t="n">
-        <v>0.7565631836744383</v>
+        <v>0.6978915595185859</v>
       </c>
       <c r="J147" s="61" t="inlineStr">
         <is>
@@ -15442,82 +15442,82 @@
       </c>
       <c r="C148" s="65" t="inlineStr">
         <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D148" s="65" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E148" s="65" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="F148" s="66" t="n">
+        <v>1.3287506e-08</v>
+      </c>
+      <c r="G148" s="64" t="inlineStr">
+        <is>
+          <t>kg Sb eq</t>
+        </is>
+      </c>
+      <c r="H148" s="67" t="n">
+        <v>0.03179673854030506</v>
+      </c>
+      <c r="I148" s="67" t="n">
+        <v>0.729688298058891</v>
+      </c>
+      <c r="J148" s="65" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="60" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B149" s="60" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="C149" s="61" t="inlineStr">
+        <is>
           <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
-      <c r="D148" s="65" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="E148" s="65" t="inlineStr">
+      <c r="D149" s="61" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E149" s="61" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F148" s="66" t="n">
-        <v>9.6234803e-09</v>
-      </c>
-      <c r="G148" s="64" t="inlineStr">
+      <c r="F149" s="62" t="n">
+        <v>1.1230718e-08</v>
+      </c>
+      <c r="G149" s="60" t="inlineStr">
         <is>
           <t>kg Sb eq</t>
         </is>
       </c>
-      <c r="H148" s="67" t="n">
-        <v>0.0230287976499786</v>
-      </c>
-      <c r="I148" s="67" t="n">
-        <v>0.7795919813244169</v>
-      </c>
-      <c r="J148" s="65" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B149" s="56" t="inlineStr">
-        <is>
-          <t>ABN</t>
-        </is>
-      </c>
-      <c r="C149" s="57" t="inlineStr">
-        <is>
-          <t>2. Wastewater Treatment Plant</t>
-        </is>
-      </c>
-      <c r="D149" s="57" t="inlineStr">
-        <is>
-          <t>Tellurium</t>
-        </is>
-      </c>
-      <c r="E149" s="57" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F149" s="58" t="n">
-        <v>8.537400399999999e-09</v>
-      </c>
-      <c r="G149" s="56" t="inlineStr">
-        <is>
-          <t>kg Sb eq</t>
-        </is>
-      </c>
-      <c r="H149" s="59" t="n">
-        <v>0.02042982997205765</v>
-      </c>
-      <c r="I149" s="59" t="n">
-        <v>0.8000218112964745</v>
-      </c>
-      <c r="J149" s="57" t="inlineStr">
-        <is>
-          <t>250</t>
+      <c r="H149" s="63" t="n">
+        <v>0.02687488561554725</v>
+      </c>
+      <c r="I149" s="63" t="n">
+        <v>0.7565631836744383</v>
+      </c>
+      <c r="J149" s="61" t="inlineStr">
+        <is>
+          <t>253</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="B150" s="64" t="inlineStr">
         <is>
-          <t>ETP Terrestrial</t>
+          <t>ABN</t>
         </is>
       </c>
       <c r="C150" s="65" t="inlineStr">
@@ -15539,77 +15539,77 @@
       </c>
       <c r="D150" s="65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E150" s="65" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="F150" s="66" t="n">
-        <v>0.21588932</v>
+        <v>9.6234803e-09</v>
       </c>
       <c r="G150" s="64" t="inlineStr">
         <is>
-          <t>kg 1,4-DCB</t>
+          <t>kg Sb eq</t>
         </is>
       </c>
       <c r="H150" s="67" t="n">
-        <v>0.4072240402863528</v>
+        <v>0.0230287976499786</v>
       </c>
       <c r="I150" s="67" t="n">
-        <v>0.4072240402863528</v>
+        <v>0.7795919813244169</v>
       </c>
       <c r="J150" s="65" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>252</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
-      <c r="A151" s="60" t="inlineStr">
+      <c r="A151" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B151" s="60" t="inlineStr">
-        <is>
-          <t>ETP Terrestrial</t>
-        </is>
-      </c>
-      <c r="C151" s="61" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D151" s="61" t="inlineStr">
-        <is>
-          <t>Antimony</t>
-        </is>
-      </c>
-      <c r="E151" s="61" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="F151" s="62" t="n">
-        <v>0.074538391</v>
-      </c>
-      <c r="G151" s="60" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H151" s="63" t="n">
-        <v>0.14059901036079</v>
-      </c>
-      <c r="I151" s="63" t="n">
-        <v>0.5478230506471429</v>
-      </c>
-      <c r="J151" s="61" t="inlineStr">
-        <is>
-          <t>335</t>
+      <c r="B151" s="56" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="C151" s="57" t="inlineStr">
+        <is>
+          <t>2. Wastewater Treatment Plant</t>
+        </is>
+      </c>
+      <c r="D151" s="57" t="inlineStr">
+        <is>
+          <t>Tellurium</t>
+        </is>
+      </c>
+      <c r="E151" s="57" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="F151" s="58" t="n">
+        <v>8.537400399999999e-09</v>
+      </c>
+      <c r="G151" s="56" t="inlineStr">
+        <is>
+          <t>kg Sb eq</t>
+        </is>
+      </c>
+      <c r="H151" s="59" t="n">
+        <v>0.02042982997205765</v>
+      </c>
+      <c r="I151" s="59" t="n">
+        <v>0.8000218112964745</v>
+      </c>
+      <c r="J151" s="57" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="C152" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D152" s="65" t="inlineStr">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="F152" s="66" t="n">
-        <v>0.06538377500000001</v>
+        <v>0.21588932</v>
       </c>
       <c r="G152" s="64" t="inlineStr">
         <is>
@@ -15648,10 +15648,10 @@
         </is>
       </c>
       <c r="H152" s="67" t="n">
-        <v>0.1233309967564576</v>
+        <v>0.4072240402863528</v>
       </c>
       <c r="I152" s="67" t="n">
-        <v>0.6711540474036004</v>
+        <v>0.4072240402863528</v>
       </c>
       <c r="J152" s="65" t="inlineStr">
         <is>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="C153" s="61" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D153" s="61" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="E153" s="61" t="inlineStr">
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="F153" s="62" t="n">
-        <v>0.032223986</v>
+        <v>0.074538391</v>
       </c>
       <c r="G153" s="60" t="inlineStr">
         <is>
@@ -15694,14 +15694,14 @@
         </is>
       </c>
       <c r="H153" s="63" t="n">
-        <v>0.0607829130827355</v>
+        <v>0.14059901036079</v>
       </c>
       <c r="I153" s="63" t="n">
-        <v>0.7319369604863359</v>
+        <v>0.5478230506471429</v>
       </c>
       <c r="J153" s="61" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>335</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="D154" s="65" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E154" s="65" t="inlineStr">
@@ -15732,7 +15732,7 @@
         </is>
       </c>
       <c r="F154" s="66" t="n">
-        <v>0.021061675</v>
+        <v>0.06538377500000001</v>
       </c>
       <c r="G154" s="64" t="inlineStr">
         <is>
@@ -15740,60 +15740,60 @@
         </is>
       </c>
       <c r="H154" s="67" t="n">
-        <v>0.03972785864858007</v>
+        <v>0.1233309967564576</v>
       </c>
       <c r="I154" s="67" t="n">
-        <v>0.771664819134916</v>
+        <v>0.6711540474036004</v>
       </c>
       <c r="J154" s="65" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>334</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
-      <c r="A155" s="56" t="inlineStr">
+      <c r="A155" s="60" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B155" s="56" t="inlineStr">
+      <c r="B155" s="60" t="inlineStr">
         <is>
           <t>ETP Terrestrial</t>
         </is>
       </c>
-      <c r="C155" s="57" t="inlineStr">
+      <c r="C155" s="61" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D155" s="57" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="E155" s="57" t="inlineStr">
+      <c r="D155" s="61" t="inlineStr">
+        <is>
+          <t>Vanadium</t>
+        </is>
+      </c>
+      <c r="E155" s="61" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="F155" s="58" t="n">
-        <v>0.020463044</v>
-      </c>
-      <c r="G155" s="56" t="inlineStr">
+      <c r="F155" s="62" t="n">
+        <v>0.032223986</v>
+      </c>
+      <c r="G155" s="60" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H155" s="59" t="n">
-        <v>0.0385986831318817</v>
-      </c>
-      <c r="I155" s="59" t="n">
-        <v>0.8102635022667978</v>
-      </c>
-      <c r="J155" s="57" t="inlineStr">
-        <is>
-          <t>338</t>
+      <c r="H155" s="63" t="n">
+        <v>0.0607829130827355</v>
+      </c>
+      <c r="I155" s="63" t="n">
+        <v>0.7319369604863359</v>
+      </c>
+      <c r="J155" s="61" t="inlineStr">
+        <is>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -15805,12 +15805,12 @@
       </c>
       <c r="B156" s="64" t="inlineStr">
         <is>
-          <t>ETP Freshwater</t>
+          <t>ETP Terrestrial</t>
         </is>
       </c>
       <c r="C156" s="65" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D156" s="65" t="inlineStr">
@@ -15820,11 +15820,11 @@
       </c>
       <c r="E156" s="65" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="F156" s="66" t="n">
-        <v>0.00021983237</v>
+        <v>0.021061675</v>
       </c>
       <c r="G156" s="64" t="inlineStr">
         <is>
@@ -15832,60 +15832,60 @@
         </is>
       </c>
       <c r="H156" s="67" t="n">
-        <v>0.358372701929054</v>
+        <v>0.03972785864858007</v>
       </c>
       <c r="I156" s="67" t="n">
-        <v>0.358372701929054</v>
+        <v>0.771664819134916</v>
       </c>
       <c r="J156" s="65" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>337</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
-      <c r="A157" s="60" t="inlineStr">
+      <c r="A157" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B157" s="60" t="inlineStr">
-        <is>
-          <t>ETP Freshwater</t>
-        </is>
-      </c>
-      <c r="C157" s="61" t="inlineStr">
+      <c r="B157" s="56" t="inlineStr">
+        <is>
+          <t>ETP Terrestrial</t>
+        </is>
+      </c>
+      <c r="C157" s="57" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D157" s="61" t="inlineStr">
-        <is>
-          <t>Carbofuran</t>
-        </is>
-      </c>
-      <c r="E157" s="61" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="F157" s="62" t="n">
-        <v>8.8438372e-05</v>
-      </c>
-      <c r="G157" s="60" t="inlineStr">
+      <c r="D157" s="57" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="E157" s="57" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F157" s="58" t="n">
+        <v>0.020463044</v>
+      </c>
+      <c r="G157" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H157" s="63" t="n">
-        <v>0.1441730275111295</v>
-      </c>
-      <c r="I157" s="63" t="n">
-        <v>0.5025457294401834</v>
-      </c>
-      <c r="J157" s="61" t="inlineStr">
-        <is>
-          <t>809</t>
+      <c r="H157" s="59" t="n">
+        <v>0.0385986831318817</v>
+      </c>
+      <c r="I157" s="59" t="n">
+        <v>0.8102635022667978</v>
+      </c>
+      <c r="J157" s="57" t="inlineStr">
+        <is>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="D158" s="65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="E158" s="65" t="inlineStr">
@@ -15916,7 +15916,7 @@
         </is>
       </c>
       <c r="F158" s="66" t="n">
-        <v>7.9509661e-05</v>
+        <v>0.00021983237</v>
       </c>
       <c r="G158" s="64" t="inlineStr">
         <is>
@@ -15924,14 +15924,14 @@
         </is>
       </c>
       <c r="H158" s="67" t="n">
-        <v>0.1296173627297614</v>
+        <v>0.358372701929054</v>
       </c>
       <c r="I158" s="67" t="n">
-        <v>0.6321630921699448</v>
+        <v>0.358372701929054</v>
       </c>
       <c r="J158" s="65" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>808</t>
         </is>
       </c>
     </row>
@@ -15953,16 +15953,16 @@
       </c>
       <c r="D159" s="61" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Carbofuran</t>
         </is>
       </c>
       <c r="E159" s="61" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="F159" s="62" t="n">
-        <v>4.8334774e-05</v>
+        <v>8.8438372e-05</v>
       </c>
       <c r="G159" s="60" t="inlineStr">
         <is>
@@ -15970,14 +15970,14 @@
         </is>
       </c>
       <c r="H159" s="63" t="n">
-        <v>0.07879578223857654</v>
+        <v>0.1441730275111295</v>
       </c>
       <c r="I159" s="63" t="n">
-        <v>0.7109588744085213</v>
+        <v>0.5025457294401834</v>
       </c>
       <c r="J159" s="61" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>809</t>
         </is>
       </c>
     </row>
@@ -15994,82 +15994,82 @@
       </c>
       <c r="C160" s="65" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D160" s="65" t="inlineStr">
         <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E160" s="65" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F160" s="66" t="n">
+        <v>7.9509661e-05</v>
+      </c>
+      <c r="G160" s="64" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H160" s="67" t="n">
+        <v>0.1296173627297614</v>
+      </c>
+      <c r="I160" s="67" t="n">
+        <v>0.6321630921699448</v>
+      </c>
+      <c r="J160" s="65" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="60" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B161" s="60" t="inlineStr">
+        <is>
+          <t>ETP Freshwater</t>
+        </is>
+      </c>
+      <c r="C161" s="61" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D161" s="61" t="inlineStr">
+        <is>
           <t>Zinc</t>
         </is>
       </c>
-      <c r="E160" s="65" t="inlineStr">
+      <c r="E161" s="61" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F160" s="66" t="n">
-        <v>3.5242415e-05</v>
-      </c>
-      <c r="G160" s="64" t="inlineStr">
+      <c r="F161" s="62" t="n">
+        <v>4.8334774e-05</v>
+      </c>
+      <c r="G161" s="60" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H160" s="67" t="n">
-        <v>0.05745250113099823</v>
-      </c>
-      <c r="I160" s="67" t="n">
-        <v>0.7684113755395195</v>
-      </c>
-      <c r="J160" s="65" t="inlineStr">
+      <c r="H161" s="63" t="n">
+        <v>0.07879578223857654</v>
+      </c>
+      <c r="I161" s="63" t="n">
+        <v>0.7109588744085213</v>
+      </c>
+      <c r="J161" s="61" t="inlineStr">
         <is>
           <t>808</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B161" s="56" t="inlineStr">
-        <is>
-          <t>ETP Freshwater</t>
-        </is>
-      </c>
-      <c r="C161" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D161" s="57" t="inlineStr">
-        <is>
-          <t>Cypermethrin</t>
-        </is>
-      </c>
-      <c r="E161" s="57" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="F161" s="58" t="n">
-        <v>3.4366789e-05</v>
-      </c>
-      <c r="G161" s="56" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H161" s="59" t="n">
-        <v>0.05602504776960596</v>
-      </c>
-      <c r="I161" s="59" t="n">
-        <v>0.8244364233091255</v>
-      </c>
-      <c r="J161" s="57" t="inlineStr">
-        <is>
-          <t>811</t>
         </is>
       </c>
     </row>
@@ -16081,12 +16081,12 @@
       </c>
       <c r="B162" s="64" t="inlineStr">
         <is>
-          <t>ETP Marine</t>
+          <t>ETP Freshwater</t>
         </is>
       </c>
       <c r="C162" s="65" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D162" s="65" t="inlineStr">
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="F162" s="66" t="n">
-        <v>0.00031338391</v>
+        <v>3.5242415e-05</v>
       </c>
       <c r="G162" s="64" t="inlineStr">
         <is>
@@ -16108,60 +16108,60 @@
         </is>
       </c>
       <c r="H162" s="67" t="n">
-        <v>0.3030367211561241</v>
+        <v>0.05745250113099823</v>
       </c>
       <c r="I162" s="67" t="n">
-        <v>0.3030367211561241</v>
+        <v>0.7684113755395195</v>
       </c>
       <c r="J162" s="65" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>808</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
-      <c r="A163" s="60" t="inlineStr">
+      <c r="A163" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B163" s="60" t="inlineStr">
-        <is>
-          <t>ETP Marine</t>
-        </is>
-      </c>
-      <c r="C163" s="61" t="inlineStr">
+      <c r="B163" s="56" t="inlineStr">
+        <is>
+          <t>ETP Freshwater</t>
+        </is>
+      </c>
+      <c r="C163" s="57" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D163" s="61" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="E163" s="61" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F163" s="62" t="n">
-        <v>0.00012996346</v>
-      </c>
-      <c r="G163" s="60" t="inlineStr">
+      <c r="D163" s="57" t="inlineStr">
+        <is>
+          <t>Cypermethrin</t>
+        </is>
+      </c>
+      <c r="E163" s="57" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="F163" s="58" t="n">
+        <v>3.4366789e-05</v>
+      </c>
+      <c r="G163" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H163" s="63" t="n">
-        <v>0.1256723766976585</v>
-      </c>
-      <c r="I163" s="63" t="n">
-        <v>0.4287090978537826</v>
-      </c>
-      <c r="J163" s="61" t="inlineStr">
-        <is>
-          <t>1282</t>
+      <c r="H163" s="59" t="n">
+        <v>0.05602504776960596</v>
+      </c>
+      <c r="I163" s="59" t="n">
+        <v>0.8244364233091255</v>
+      </c>
+      <c r="J163" s="57" t="inlineStr">
+        <is>
+          <t>811</t>
         </is>
       </c>
     </row>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="D164" s="65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="E164" s="65" t="inlineStr">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="F164" s="66" t="n">
-        <v>9.4868274e-05</v>
+        <v>0.00031338391</v>
       </c>
       <c r="G164" s="64" t="inlineStr">
         <is>
@@ -16200,14 +16200,14 @@
         </is>
       </c>
       <c r="H164" s="67" t="n">
-        <v>0.09173594998767098</v>
+        <v>0.3030367211561241</v>
       </c>
       <c r="I164" s="67" t="n">
-        <v>0.5204450478414535</v>
+        <v>0.3030367211561241</v>
       </c>
       <c r="J164" s="65" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1282</t>
         </is>
       </c>
     </row>
@@ -16224,21 +16224,21 @@
       </c>
       <c r="C165" s="61" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D165" s="61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="E165" s="61" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F165" s="62" t="n">
-        <v>9.0625705e-05</v>
+        <v>0.00012996346</v>
       </c>
       <c r="G165" s="60" t="inlineStr">
         <is>
@@ -16246,14 +16246,14 @@
         </is>
       </c>
       <c r="H165" s="63" t="n">
-        <v>0.08763346049151714</v>
+        <v>0.1256723766976585</v>
       </c>
       <c r="I165" s="63" t="n">
-        <v>0.6080785083329706</v>
+        <v>0.4287090978537826</v>
       </c>
       <c r="J165" s="61" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
     </row>
@@ -16270,21 +16270,21 @@
       </c>
       <c r="C166" s="65" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D166" s="65" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E166" s="65" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F166" s="66" t="n">
-        <v>6.2608629e-05</v>
+        <v>9.4868274e-05</v>
       </c>
       <c r="G166" s="64" t="inlineStr">
         <is>
@@ -16292,14 +16292,14 @@
         </is>
       </c>
       <c r="H166" s="67" t="n">
-        <v>0.06054144148064343</v>
+        <v>0.09173594998767098</v>
       </c>
       <c r="I166" s="67" t="n">
-        <v>0.6686199498136141</v>
+        <v>0.5204450478414535</v>
       </c>
       <c r="J166" s="65" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1284</t>
         </is>
       </c>
     </row>
@@ -16321,16 +16321,16 @@
       </c>
       <c r="D167" s="61" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E167" s="61" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="F167" s="62" t="n">
-        <v>5.8122803e-05</v>
+        <v>9.0625705e-05</v>
       </c>
       <c r="G167" s="60" t="inlineStr">
         <is>
@@ -16338,14 +16338,14 @@
         </is>
       </c>
       <c r="H167" s="63" t="n">
-        <v>0.05620372675011725</v>
+        <v>0.08763346049151714</v>
       </c>
       <c r="I167" s="63" t="n">
-        <v>0.7248236765637313</v>
+        <v>0.6080785083329706</v>
       </c>
       <c r="J167" s="61" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1283</t>
         </is>
       </c>
     </row>
@@ -16362,12 +16362,12 @@
       </c>
       <c r="C168" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D168" s="65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="E168" s="65" t="inlineStr">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="F168" s="66" t="n">
-        <v>2.7409279e-05</v>
+        <v>6.2608629e-05</v>
       </c>
       <c r="G168" s="64" t="inlineStr">
         <is>
@@ -16384,14 +16384,14 @@
         </is>
       </c>
       <c r="H168" s="67" t="n">
-        <v>0.02650429001735733</v>
+        <v>0.06054144148064343</v>
       </c>
       <c r="I168" s="67" t="n">
-        <v>0.7513279665810886</v>
+        <v>0.6686199498136141</v>
       </c>
       <c r="J168" s="65" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1285</t>
         </is>
       </c>
     </row>
@@ -16408,82 +16408,82 @@
       </c>
       <c r="C169" s="61" t="inlineStr">
         <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D169" s="61" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="E169" s="61" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F169" s="62" t="n">
+        <v>5.8122803e-05</v>
+      </c>
+      <c r="G169" s="60" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H169" s="63" t="n">
+        <v>0.05620372675011725</v>
+      </c>
+      <c r="I169" s="63" t="n">
+        <v>0.7248236765637313</v>
+      </c>
+      <c r="J169" s="61" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="64" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B170" s="64" t="inlineStr">
+        <is>
+          <t>ETP Marine</t>
+        </is>
+      </c>
+      <c r="C170" s="65" t="inlineStr">
+        <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D169" s="61" t="inlineStr">
-        <is>
-          <t>Cypermethrin</t>
-        </is>
-      </c>
-      <c r="E169" s="61" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="F169" s="62" t="n">
-        <v>2.7217269e-05</v>
-      </c>
-      <c r="G169" s="60" t="inlineStr">
+      <c r="D170" s="65" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E170" s="65" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F170" s="66" t="n">
+        <v>2.7409279e-05</v>
+      </c>
+      <c r="G170" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H169" s="63" t="n">
-        <v>0.02631861972934163</v>
-      </c>
-      <c r="I169" s="63" t="n">
-        <v>0.7776465863104303</v>
-      </c>
-      <c r="J169" s="61" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B170" s="56" t="inlineStr">
-        <is>
-          <t>ETP Marine</t>
-        </is>
-      </c>
-      <c r="C170" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D170" s="57" t="inlineStr">
-        <is>
-          <t>Vanadium</t>
-        </is>
-      </c>
-      <c r="E170" s="57" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="F170" s="58" t="n">
-        <v>2.6534249e-05</v>
-      </c>
-      <c r="G170" s="56" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H170" s="59" t="n">
-        <v>0.02565815141977189</v>
-      </c>
-      <c r="I170" s="59" t="n">
-        <v>0.8033047377302022</v>
-      </c>
-      <c r="J170" s="57" t="inlineStr">
-        <is>
-          <t>1286</t>
+      <c r="H170" s="67" t="n">
+        <v>0.02650429001735733</v>
+      </c>
+      <c r="I170" s="67" t="n">
+        <v>0.7513279665810886</v>
+      </c>
+      <c r="J170" s="65" t="inlineStr">
+        <is>
+          <t>1283</t>
         </is>
       </c>
     </row>
@@ -16495,26 +16495,26 @@
       </c>
       <c r="B171" s="60" t="inlineStr">
         <is>
-          <t>HTC</t>
+          <t>ETP Marine</t>
         </is>
       </c>
       <c r="C171" s="61" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D171" s="61" t="inlineStr">
         <is>
-          <t>Chromium VI</t>
+          <t>Cypermethrin</t>
         </is>
       </c>
       <c r="E171" s="61" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="F171" s="62" t="n">
-        <v>0.00077327147</v>
+        <v>2.7217269e-05</v>
       </c>
       <c r="G171" s="60" t="inlineStr">
         <is>
@@ -16522,60 +16522,60 @@
         </is>
       </c>
       <c r="H171" s="63" t="n">
-        <v>0.4664965366497134</v>
+        <v>0.02631861972934163</v>
       </c>
       <c r="I171" s="63" t="n">
-        <v>0.4664965366497134</v>
+        <v>0.7776465863104303</v>
       </c>
       <c r="J171" s="61" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1288</t>
         </is>
       </c>
     </row>
     <row r="172" ht="30" customHeight="1">
-      <c r="A172" s="64" t="inlineStr">
+      <c r="A172" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B172" s="64" t="inlineStr">
-        <is>
-          <t>HTC</t>
-        </is>
-      </c>
-      <c r="C172" s="65" t="inlineStr">
+      <c r="B172" s="56" t="inlineStr">
+        <is>
+          <t>ETP Marine</t>
+        </is>
+      </c>
+      <c r="C172" s="57" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D172" s="65" t="inlineStr">
-        <is>
-          <t>Chromium VI</t>
-        </is>
-      </c>
-      <c r="E172" s="65" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F172" s="66" t="n">
-        <v>0.00036482467</v>
-      </c>
-      <c r="G172" s="64" t="inlineStr">
+      <c r="D172" s="57" t="inlineStr">
+        <is>
+          <t>Vanadium</t>
+        </is>
+      </c>
+      <c r="E172" s="57" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="F172" s="58" t="n">
+        <v>2.6534249e-05</v>
+      </c>
+      <c r="G172" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H172" s="67" t="n">
-        <v>0.2200901645050665</v>
-      </c>
-      <c r="I172" s="67" t="n">
-        <v>0.6865867011547799</v>
-      </c>
-      <c r="J172" s="65" t="inlineStr">
-        <is>
-          <t>1756</t>
+      <c r="H172" s="59" t="n">
+        <v>0.02565815141977189</v>
+      </c>
+      <c r="I172" s="59" t="n">
+        <v>0.8033047377302022</v>
+      </c>
+      <c r="J172" s="57" t="inlineStr">
+        <is>
+          <t>1286</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="C173" s="61" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D173" s="61" t="inlineStr">
@@ -16606,7 +16606,7 @@
         </is>
       </c>
       <c r="F173" s="62" t="n">
-        <v>0.00017227924</v>
+        <v>0.00077327147</v>
       </c>
       <c r="G173" s="60" t="inlineStr">
         <is>
@@ -16614,10 +16614,10 @@
         </is>
       </c>
       <c r="H173" s="63" t="n">
-        <v>0.1039320237647521</v>
+        <v>0.4664965366497134</v>
       </c>
       <c r="I173" s="63" t="n">
-        <v>0.790518724919532</v>
+        <v>0.4664965366497134</v>
       </c>
       <c r="J173" s="61" t="inlineStr">
         <is>
@@ -16626,48 +16626,48 @@
       </c>
     </row>
     <row r="174" ht="30" customHeight="1">
-      <c r="A174" s="56" t="inlineStr">
+      <c r="A174" s="64" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B174" s="56" t="inlineStr">
+      <c r="B174" s="64" t="inlineStr">
         <is>
           <t>HTC</t>
         </is>
       </c>
-      <c r="C174" s="57" t="inlineStr">
-        <is>
-          <t>7. Hazardous Waste Treatment System</t>
-        </is>
-      </c>
-      <c r="D174" s="57" t="inlineStr">
-        <is>
-          <t>Arsenic</t>
-        </is>
-      </c>
-      <c r="E174" s="57" t="inlineStr">
+      <c r="C174" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D174" s="65" t="inlineStr">
+        <is>
+          <t>Chromium VI</t>
+        </is>
+      </c>
+      <c r="E174" s="65" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F174" s="58" t="n">
-        <v>5.1598111e-05</v>
-      </c>
-      <c r="G174" s="56" t="inlineStr">
+      <c r="F174" s="66" t="n">
+        <v>0.00036482467</v>
+      </c>
+      <c r="G174" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H174" s="59" t="n">
-        <v>0.03112792985776066</v>
-      </c>
-      <c r="I174" s="59" t="n">
-        <v>0.8216466547772927</v>
-      </c>
-      <c r="J174" s="57" t="inlineStr">
-        <is>
-          <t>1757</t>
+      <c r="H174" s="67" t="n">
+        <v>0.2200901645050665</v>
+      </c>
+      <c r="I174" s="67" t="n">
+        <v>0.6865867011547799</v>
+      </c>
+      <c r="J174" s="65" t="inlineStr">
+        <is>
+          <t>1756</t>
         </is>
       </c>
     </row>
@@ -16679,317 +16679,317 @@
       </c>
       <c r="B175" s="60" t="inlineStr">
         <is>
+          <t>HTC</t>
+        </is>
+      </c>
+      <c r="C175" s="61" t="inlineStr">
+        <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D175" s="61" t="inlineStr">
+        <is>
+          <t>Chromium VI</t>
+        </is>
+      </c>
+      <c r="E175" s="61" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F175" s="62" t="n">
+        <v>0.00017227924</v>
+      </c>
+      <c r="G175" s="60" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H175" s="63" t="n">
+        <v>0.1039320237647521</v>
+      </c>
+      <c r="I175" s="63" t="n">
+        <v>0.790518724919532</v>
+      </c>
+      <c r="J175" s="61" t="inlineStr">
+        <is>
+          <t>1756</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="56" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B176" s="56" t="inlineStr">
+        <is>
+          <t>HTC</t>
+        </is>
+      </c>
+      <c r="C176" s="57" t="inlineStr">
+        <is>
+          <t>7. Hazardous Waste Treatment System</t>
+        </is>
+      </c>
+      <c r="D176" s="57" t="inlineStr">
+        <is>
+          <t>Arsenic</t>
+        </is>
+      </c>
+      <c r="E176" s="57" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F176" s="58" t="n">
+        <v>5.1598111e-05</v>
+      </c>
+      <c r="G176" s="56" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H176" s="59" t="n">
+        <v>0.03112792985776066</v>
+      </c>
+      <c r="I176" s="59" t="n">
+        <v>0.8216466547772927</v>
+      </c>
+      <c r="J176" s="57" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="60" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B177" s="60" t="inlineStr">
+        <is>
           <t>HTN</t>
         </is>
       </c>
-      <c r="C175" s="61" t="inlineStr">
+      <c r="C177" s="61" t="inlineStr">
         <is>
           <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
-      <c r="D175" s="61" t="inlineStr">
+      <c r="D177" s="61" t="inlineStr">
         <is>
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="E175" s="61" t="inlineStr">
+      <c r="E177" s="61" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F175" s="62" t="n">
+      <c r="F177" s="62" t="n">
         <v>0.013071522</v>
       </c>
-      <c r="G175" s="60" t="inlineStr">
+      <c r="G177" s="60" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H175" s="63" t="n">
+      <c r="H177" s="63" t="n">
         <v>0.4669507053921276</v>
       </c>
-      <c r="I175" s="63" t="n">
+      <c r="I177" s="63" t="n">
         <v>0.4669507053921276</v>
       </c>
-      <c r="J175" s="61" t="inlineStr">
+      <c r="J177" s="61" t="inlineStr">
         <is>
           <t>1888</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="30" customHeight="1">
-      <c r="A176" s="64" t="inlineStr">
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="64" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B176" s="64" t="inlineStr">
+      <c r="B178" s="64" t="inlineStr">
         <is>
           <t>HTN</t>
         </is>
       </c>
-      <c r="C176" s="65" t="inlineStr">
+      <c r="C178" s="65" t="inlineStr">
         <is>
           <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
-      <c r="D176" s="65" t="inlineStr">
+      <c r="D178" s="65" t="inlineStr">
         <is>
           <t>Zinc</t>
         </is>
       </c>
-      <c r="E176" s="65" t="inlineStr">
+      <c r="E178" s="65" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F176" s="66" t="n">
+      <c r="F178" s="66" t="n">
         <v>0.0085867689</v>
       </c>
-      <c r="G176" s="64" t="inlineStr">
+      <c r="G178" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H176" s="67" t="n">
+      <c r="H178" s="67" t="n">
         <v>0.3067429940365157</v>
       </c>
-      <c r="I176" s="67" t="n">
+      <c r="I178" s="67" t="n">
         <v>0.7736936994286432</v>
       </c>
-      <c r="J176" s="65" t="inlineStr">
+      <c r="J178" s="65" t="inlineStr">
         <is>
           <t>1889</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="30" customHeight="1">
-      <c r="A177" s="56" t="inlineStr">
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B177" s="56" t="inlineStr">
+      <c r="B179" s="56" t="inlineStr">
         <is>
           <t>HTN</t>
         </is>
       </c>
-      <c r="C177" s="57" t="inlineStr">
+      <c r="C179" s="57" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D177" s="57" t="inlineStr">
+      <c r="D179" s="57" t="inlineStr">
         <is>
           <t>Zinc</t>
         </is>
       </c>
-      <c r="E177" s="57" t="inlineStr">
+      <c r="E179" s="57" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F177" s="58" t="n">
+      <c r="F179" s="58" t="n">
         <v>0.0019483272</v>
       </c>
-      <c r="G177" s="56" t="inlineStr">
+      <c r="G179" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H177" s="59" t="n">
+      <c r="H179" s="59" t="n">
         <v>0.06959960442056165</v>
       </c>
-      <c r="I177" s="59" t="n">
+      <c r="I179" s="59" t="n">
         <v>0.8432933038492049</v>
       </c>
-      <c r="J177" s="57" t="inlineStr">
+      <c r="J179" s="57" t="inlineStr">
         <is>
           <t>1889</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="56" t="inlineStr">
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B178" s="56" t="inlineStr">
+      <c r="B180" s="56" t="inlineStr">
         <is>
           <t>WSF</t>
         </is>
       </c>
-      <c r="C178" s="57" t="inlineStr">
+      <c r="C180" s="57" t="inlineStr">
         <is>
           <t>2. Wastewater Treatment Plant</t>
         </is>
       </c>
-      <c r="D178" s="57" t="inlineStr">
+      <c r="D180" s="57" t="inlineStr">
         <is>
           <t>Waste water/m3</t>
         </is>
       </c>
-      <c r="E178" s="57" t="inlineStr">
+      <c r="E180" s="57" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="F178" s="58" t="n">
+      <c r="F180" s="58" t="n">
         <v>-32.117591</v>
       </c>
-      <c r="G178" s="56" t="inlineStr">
+      <c r="G180" s="56" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="H178" s="59" t="n">
+      <c r="H180" s="59" t="n">
         <v>-1.001042165550009</v>
       </c>
-      <c r="I178" s="59" t="n">
+      <c r="I180" s="59" t="n">
         <v>1.001042165550009</v>
       </c>
-      <c r="J178" s="57" t="inlineStr">
+      <c r="J180" s="57" t="inlineStr">
         <is>
           <t>2275</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="30" customHeight="1">
-      <c r="A179" s="60" t="inlineStr">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="60" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B179" s="60" t="inlineStr">
+      <c r="B181" s="60" t="inlineStr">
         <is>
           <t>LUC</t>
         </is>
       </c>
-      <c r="C179" s="61" t="inlineStr">
+      <c r="C181" s="61" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D179" s="61" t="inlineStr">
+      <c r="D181" s="61" t="inlineStr">
         <is>
           <t>Occupation, permanent crop</t>
         </is>
       </c>
-      <c r="E179" s="61" t="inlineStr">
+      <c r="E181" s="61" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F179" s="62" t="n">
+      <c r="F181" s="62" t="n">
         <v>0.029833288</v>
       </c>
-      <c r="G179" s="60" t="inlineStr">
+      <c r="G181" s="60" t="inlineStr">
         <is>
           <t>m2a crop eq</t>
         </is>
       </c>
-      <c r="H179" s="63" t="n">
+      <c r="H181" s="63" t="n">
         <v>0.461481144184372</v>
       </c>
-      <c r="I179" s="63" t="n">
+      <c r="I181" s="63" t="n">
         <v>0.461481144184372</v>
       </c>
-      <c r="J179" s="61" t="inlineStr">
+      <c r="J181" s="61" t="inlineStr">
         <is>
           <t>2212</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="64" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B180" s="64" t="inlineStr">
-        <is>
-          <t>LUC</t>
-        </is>
-      </c>
-      <c r="C180" s="65" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D180" s="65" t="inlineStr">
-        <is>
-          <t>Transformation, from forest, secondary (non-use)</t>
-        </is>
-      </c>
-      <c r="E180" s="65" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F180" s="66" t="n">
-        <v>0.018638119</v>
-      </c>
-      <c r="G180" s="64" t="inlineStr">
-        <is>
-          <t>m2a crop eq</t>
-        </is>
-      </c>
-      <c r="H180" s="67" t="n">
-        <v>0.2883068229544288</v>
-      </c>
-      <c r="I180" s="67" t="n">
-        <v>0.7497879671388008</v>
-      </c>
-      <c r="J180" s="65" t="inlineStr">
-        <is>
-          <t>2213</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="30" customHeight="1">
-      <c r="A181" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B181" s="56" t="inlineStr">
-        <is>
-          <t>LUC</t>
-        </is>
-      </c>
-      <c r="C181" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D181" s="57" t="inlineStr">
-        <is>
-          <t>Transformation, from forest, primary (non-use)</t>
-        </is>
-      </c>
-      <c r="E181" s="57" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F181" s="58" t="n">
-        <v>0.0048062854</v>
-      </c>
-      <c r="G181" s="56" t="inlineStr">
-        <is>
-          <t>m2a crop eq</t>
-        </is>
-      </c>
-      <c r="H181" s="59" t="n">
-        <v>0.07434681975612752</v>
-      </c>
-      <c r="I181" s="59" t="n">
-        <v>0.8241347868949284</v>
-      </c>
-      <c r="J181" s="57" t="inlineStr">
-        <is>
-          <t>2214</t>
         </is>
       </c>
     </row>
@@ -17001,7 +17001,7 @@
       </c>
       <c r="B182" s="64" t="inlineStr">
         <is>
-          <t>CEN</t>
+          <t>LUC</t>
         </is>
       </c>
       <c r="C182" s="65" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="D182" s="65" t="inlineStr">
         <is>
-          <t>Oil, crude</t>
+          <t>Transformation, from forest, secondary (non-use)</t>
         </is>
       </c>
       <c r="E182" s="65" t="inlineStr">
@@ -17020,68 +17020,68 @@
         </is>
       </c>
       <c r="F182" s="66" t="n">
-        <v>2.2492076</v>
+        <v>0.018638119</v>
       </c>
       <c r="G182" s="64" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>m2a crop eq</t>
         </is>
       </c>
       <c r="H182" s="67" t="n">
-        <v>0.6589086844914374</v>
+        <v>0.2883068229544288</v>
       </c>
       <c r="I182" s="67" t="n">
-        <v>0.6589086844914374</v>
+        <v>0.7497879671388008</v>
       </c>
       <c r="J182" s="65" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2213</t>
         </is>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="60" t="inlineStr">
+      <c r="A183" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B183" s="60" t="inlineStr">
-        <is>
-          <t>CEN</t>
-        </is>
-      </c>
-      <c r="C183" s="61" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D183" s="61" t="inlineStr">
-        <is>
-          <t>Oil, crude</t>
-        </is>
-      </c>
-      <c r="E183" s="61" t="inlineStr">
+      <c r="B183" s="56" t="inlineStr">
+        <is>
+          <t>LUC</t>
+        </is>
+      </c>
+      <c r="C183" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D183" s="57" t="inlineStr">
+        <is>
+          <t>Transformation, from forest, primary (non-use)</t>
+        </is>
+      </c>
+      <c r="E183" s="57" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F183" s="62" t="n">
-        <v>0.25937731</v>
-      </c>
-      <c r="G183" s="60" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H183" s="63" t="n">
-        <v>0.07598496560256499</v>
-      </c>
-      <c r="I183" s="63" t="n">
-        <v>0.7348936500940023</v>
-      </c>
-      <c r="J183" s="61" t="inlineStr">
-        <is>
-          <t>2923</t>
+      <c r="F183" s="58" t="n">
+        <v>0.0048062854</v>
+      </c>
+      <c r="G183" s="56" t="inlineStr">
+        <is>
+          <t>m2a crop eq</t>
+        </is>
+      </c>
+      <c r="H183" s="59" t="n">
+        <v>0.07434681975612752</v>
+      </c>
+      <c r="I183" s="59" t="n">
+        <v>0.8241347868949284</v>
+      </c>
+      <c r="J183" s="57" t="inlineStr">
+        <is>
+          <t>2214</t>
         </is>
       </c>
     </row>
@@ -17103,177 +17103,181 @@
       </c>
       <c r="D184" s="65" t="inlineStr">
         <is>
+          <t>Oil, crude</t>
+        </is>
+      </c>
+      <c r="E184" s="65" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="F184" s="66" t="n">
+        <v>2.2492076</v>
+      </c>
+      <c r="G184" s="64" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H184" s="67" t="n">
+        <v>0.6589086844914374</v>
+      </c>
+      <c r="I184" s="67" t="n">
+        <v>0.6589086844914374</v>
+      </c>
+      <c r="J184" s="65" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="60" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B185" s="60" t="inlineStr">
+        <is>
+          <t>CEN</t>
+        </is>
+      </c>
+      <c r="C185" s="61" t="inlineStr">
+        <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D185" s="61" t="inlineStr">
+        <is>
+          <t>Oil, crude</t>
+        </is>
+      </c>
+      <c r="E185" s="61" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="F185" s="62" t="n">
+        <v>0.25937731</v>
+      </c>
+      <c r="G185" s="60" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H185" s="63" t="n">
+        <v>0.07598496560256499</v>
+      </c>
+      <c r="I185" s="63" t="n">
+        <v>0.7348936500940023</v>
+      </c>
+      <c r="J185" s="61" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="64" t="inlineStr">
+        <is>
+          <t>LCI UT LMO</t>
+        </is>
+      </c>
+      <c r="B186" s="64" t="inlineStr">
+        <is>
+          <t>CEN</t>
+        </is>
+      </c>
+      <c r="C186" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D186" s="65" t="inlineStr">
+        <is>
           <t>Gas, natural/m3</t>
         </is>
       </c>
-      <c r="E184" s="65" t="inlineStr">
+      <c r="E186" s="65" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F184" s="66" t="n">
+      <c r="F186" s="66" t="n">
         <v>0.19444802</v>
       </c>
-      <c r="G184" s="64" t="inlineStr">
+      <c r="G186" s="64" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H184" s="67" t="n">
+      <c r="H186" s="67" t="n">
         <v>0.05696383431221053</v>
       </c>
-      <c r="I184" s="67" t="n">
+      <c r="I186" s="67" t="n">
         <v>0.7918574844062128</v>
       </c>
-      <c r="J184" s="65" t="inlineStr">
+      <c r="J186" s="65" t="inlineStr">
         <is>
           <t>2924</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="56" t="inlineStr">
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="56" t="inlineStr">
         <is>
           <t>LCI UT LMO</t>
         </is>
       </c>
-      <c r="B185" s="56" t="inlineStr">
+      <c r="B187" s="56" t="inlineStr">
         <is>
           <t>CEN</t>
         </is>
       </c>
-      <c r="C185" s="57" t="inlineStr">
+      <c r="C187" s="57" t="inlineStr">
         <is>
           <t>2. Wastewater Treatment Plant</t>
         </is>
       </c>
-      <c r="D185" s="57" t="inlineStr">
+      <c r="D187" s="57" t="inlineStr">
         <is>
           <t>Oil, crude</t>
         </is>
       </c>
-      <c r="E185" s="57" t="inlineStr">
+      <c r="E187" s="57" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="F185" s="58" t="n">
+      <c r="F187" s="58" t="n">
         <v>0.19087223</v>
       </c>
-      <c r="G185" s="56" t="inlineStr">
+      <c r="G187" s="56" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H185" s="59" t="n">
+      <c r="H187" s="59" t="n">
         <v>0.05591630135664091</v>
       </c>
-      <c r="I185" s="59" t="n">
+      <c r="I187" s="59" t="n">
         <v>0.8477737857628538</v>
       </c>
-      <c r="J185" s="57" t="inlineStr">
+      <c r="J187" s="57" t="inlineStr">
         <is>
           <t>2923</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="30" customHeight="1">
-      <c r="A186" s="56" t="inlineStr">
-        <is>
-          <t>LCI UT LMO</t>
-        </is>
-      </c>
-      <c r="B186" s="56" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="C186" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D186" s="57" t="inlineStr">
-        <is>
-          <t>Energy, gross calorific value, in biomass</t>
-        </is>
-      </c>
-      <c r="E186" s="57" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="F186" s="58" t="n">
-        <v>1.9673801</v>
-      </c>
-      <c r="G186" s="56" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H186" s="59" t="n">
-        <v>0.8727386797510129</v>
-      </c>
-      <c r="I186" s="59" t="n">
-        <v>0.8727386797510129</v>
-      </c>
-      <c r="J186" s="57" t="inlineStr">
-        <is>
-          <t>2988</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="30" customHeight="1">
-      <c r="A187" s="60" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B187" s="60" t="inlineStr">
-        <is>
-          <t>GWP</t>
-        </is>
-      </c>
-      <c r="C187" s="61" t="inlineStr">
-        <is>
-          <t>7. Hazardous Waste Treatment System</t>
-        </is>
-      </c>
-      <c r="D187" s="61" t="inlineStr">
-        <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E187" s="61" t="inlineStr"/>
-      <c r="F187" s="62" t="n">
-        <v>0.32054936</v>
-      </c>
-      <c r="G187" s="60" t="inlineStr">
-        <is>
-          <t>kg CO2-eq</t>
-        </is>
-      </c>
-      <c r="H187" s="63" t="n">
-        <v>0.4868700802937016</v>
-      </c>
-      <c r="I187" s="63" t="n">
-        <v>0.4868700802937016</v>
-      </c>
-      <c r="J187" s="61" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="56" t="inlineStr">
         <is>
-          <t>PROC UT LMO</t>
+          <t>LCI UT LMO</t>
         </is>
       </c>
       <c r="B188" s="56" t="inlineStr">
         <is>
-          <t>GWP</t>
+          <t>CED</t>
         </is>
       </c>
       <c r="C188" s="57" t="inlineStr">
@@ -17283,27 +17287,31 @@
       </c>
       <c r="D188" s="57" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="E188" s="57" t="inlineStr"/>
+          <t>Energy, gross calorific value, in biomass</t>
+        </is>
+      </c>
+      <c r="E188" s="57" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
       <c r="F188" s="58" t="n">
-        <v>0.23355677</v>
+        <v>1.9673801</v>
       </c>
       <c r="G188" s="56" t="inlineStr">
         <is>
-          <t>kg CO2-eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H188" s="59" t="n">
-        <v>0.3547403849536234</v>
+        <v>0.8727386797510129</v>
       </c>
       <c r="I188" s="59" t="n">
-        <v>0.841610465247325</v>
+        <v>0.8727386797510129</v>
       </c>
       <c r="J188" s="57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2988</t>
         </is>
       </c>
     </row>
@@ -17315,37 +17323,37 @@
       </c>
       <c r="B189" s="60" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C189" s="61" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D189" s="61" t="inlineStr">
         <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
         </is>
       </c>
       <c r="E189" s="61" t="inlineStr"/>
       <c r="F189" s="62" t="n">
-        <v>2.8618062e-08</v>
+        <v>0.32054936</v>
       </c>
       <c r="G189" s="60" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H189" s="63" t="n">
-        <v>0.7299140487133552</v>
+        <v>0.4868700802937016</v>
       </c>
       <c r="I189" s="63" t="n">
-        <v>0.7299140487133552</v>
+        <v>0.4868700802937016</v>
       </c>
       <c r="J189" s="61" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -17357,37 +17365,37 @@
       </c>
       <c r="B190" s="56" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C190" s="57" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D190" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="E190" s="57" t="inlineStr"/>
       <c r="F190" s="58" t="n">
-        <v>3.1288453e-09</v>
+        <v>0.23355677</v>
       </c>
       <c r="G190" s="56" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H190" s="59" t="n">
-        <v>0.07980233394982346</v>
+        <v>0.3547403849536234</v>
       </c>
       <c r="I190" s="59" t="n">
-        <v>0.8097163826631787</v>
+        <v>0.841610465247325</v>
       </c>
       <c r="J190" s="57" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -17399,37 +17407,37 @@
       </c>
       <c r="B191" s="60" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="C191" s="61" t="inlineStr">
         <is>
-          <t>3. Workshop</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D191" s="61" t="inlineStr">
         <is>
-          <t>3. Workshop</t>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E191" s="61" t="inlineStr"/>
       <c r="F191" s="62" t="n">
-        <v>0.001986004</v>
+        <v>2.8618062e-08</v>
       </c>
       <c r="G191" s="60" t="inlineStr">
         <is>
-          <t>kg SO2 eq</t>
+          <t>kg CFC-11 eq</t>
         </is>
       </c>
       <c r="H191" s="63" t="n">
-        <v>0.4823761461055625</v>
+        <v>0.7299140487133552</v>
       </c>
       <c r="I191" s="63" t="n">
-        <v>0.4823761461055625</v>
+        <v>0.7299140487133552</v>
       </c>
       <c r="J191" s="61" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -17441,37 +17449,37 @@
       </c>
       <c r="B192" s="56" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="C192" s="57" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D192" s="57" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
       <c r="E192" s="57" t="inlineStr"/>
       <c r="F192" s="58" t="n">
-        <v>0.0013355887</v>
+        <v>3.1288453e-09</v>
       </c>
       <c r="G192" s="56" t="inlineStr">
         <is>
-          <t>kg SO2 eq</t>
+          <t>kg CFC-11 eq</t>
         </is>
       </c>
       <c r="H192" s="59" t="n">
-        <v>0.3243982035726707</v>
+        <v>0.07980233394982346</v>
       </c>
       <c r="I192" s="59" t="n">
-        <v>0.8067743496782331</v>
+        <v>0.8097163826631787</v>
       </c>
       <c r="J192" s="57" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -17483,7 +17491,7 @@
       </c>
       <c r="B193" s="60" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C193" s="61" t="inlineStr">
@@ -17498,106 +17506,106 @@
       </c>
       <c r="E193" s="61" t="inlineStr"/>
       <c r="F193" s="62" t="n">
+        <v>0.001986004</v>
+      </c>
+      <c r="G193" s="60" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H193" s="63" t="n">
+        <v>0.4823761461055625</v>
+      </c>
+      <c r="I193" s="63" t="n">
+        <v>0.4823761461055625</v>
+      </c>
+      <c r="J193" s="61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B194" s="56" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C194" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D194" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="E194" s="57" t="inlineStr"/>
+      <c r="F194" s="58" t="n">
+        <v>0.0013355887</v>
+      </c>
+      <c r="G194" s="56" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H194" s="59" t="n">
+        <v>0.3243982035726707</v>
+      </c>
+      <c r="I194" s="59" t="n">
+        <v>0.8067743496782331</v>
+      </c>
+      <c r="J194" s="57" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="60" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B195" s="60" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C195" s="61" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="D195" s="61" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="E195" s="61" t="inlineStr"/>
+      <c r="F195" s="62" t="n">
         <v>0.00043415559</v>
       </c>
-      <c r="G193" s="60" t="inlineStr">
+      <c r="G195" s="60" t="inlineStr">
         <is>
           <t>kg PO4--- eq</t>
         </is>
       </c>
-      <c r="H193" s="63" t="n">
+      <c r="H195" s="63" t="n">
         <v>0.4625634279869507</v>
       </c>
-      <c r="I193" s="63" t="n">
+      <c r="I195" s="63" t="n">
         <v>0.4625634279869507</v>
       </c>
-      <c r="J193" s="61" t="inlineStr">
+      <c r="J195" s="61" t="inlineStr">
         <is>
           <t>141</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="64" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B194" s="64" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C194" s="65" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D194" s="65" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E194" s="65" t="inlineStr"/>
-      <c r="F194" s="66" t="n">
-        <v>0.00029558722</v>
-      </c>
-      <c r="G194" s="64" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H194" s="67" t="n">
-        <v>0.3149281983270857</v>
-      </c>
-      <c r="I194" s="67" t="n">
-        <v>0.7774916263140363</v>
-      </c>
-      <c r="J194" s="65" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="30" customHeight="1">
-      <c r="A195" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B195" s="56" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C195" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D195" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="E195" s="57" t="inlineStr"/>
-      <c r="F195" s="58" t="n">
-        <v>9.1201674e-05</v>
-      </c>
-      <c r="G195" s="56" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H195" s="59" t="n">
-        <v>0.09716921752311965</v>
-      </c>
-      <c r="I195" s="59" t="n">
-        <v>0.874660843837156</v>
-      </c>
-      <c r="J195" s="57" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17617,7 @@
       </c>
       <c r="B196" s="64" t="inlineStr">
         <is>
-          <t>POFP</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C196" s="65" t="inlineStr">
@@ -17619,111 +17627,111 @@
       </c>
       <c r="D196" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E196" s="65" t="inlineStr"/>
       <c r="F196" s="66" t="n">
+        <v>0.00029558722</v>
+      </c>
+      <c r="G196" s="64" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H196" s="67" t="n">
+        <v>0.3149281983270857</v>
+      </c>
+      <c r="I196" s="67" t="n">
+        <v>0.7774916263140363</v>
+      </c>
+      <c r="J196" s="65" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B197" s="56" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C197" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D197" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="E197" s="57" t="inlineStr"/>
+      <c r="F197" s="58" t="n">
+        <v>9.1201674e-05</v>
+      </c>
+      <c r="G197" s="56" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H197" s="59" t="n">
+        <v>0.09716921752311965</v>
+      </c>
+      <c r="I197" s="59" t="n">
+        <v>0.874660843837156</v>
+      </c>
+      <c r="J197" s="57" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="64" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B198" s="64" t="inlineStr">
+        <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="C198" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D198" s="65" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="E198" s="65" t="inlineStr"/>
+      <c r="F198" s="66" t="n">
         <v>0.00010155903</v>
       </c>
-      <c r="G196" s="64" t="inlineStr">
+      <c r="G198" s="64" t="inlineStr">
         <is>
           <t>kg C2H4 eq</t>
         </is>
       </c>
-      <c r="H196" s="67" t="n">
+      <c r="H198" s="67" t="n">
         <v>0.4693583178288633</v>
       </c>
-      <c r="I196" s="67" t="n">
+      <c r="I198" s="67" t="n">
         <v>0.4693583178288633</v>
       </c>
-      <c r="J196" s="65" t="inlineStr">
+      <c r="J198" s="65" t="inlineStr">
         <is>
           <t>182</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="60" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B197" s="60" t="inlineStr">
-        <is>
-          <t>POFP</t>
-        </is>
-      </c>
-      <c r="C197" s="61" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D197" s="61" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E197" s="61" t="inlineStr"/>
-      <c r="F197" s="62" t="n">
-        <v>5.4613836e-05</v>
-      </c>
-      <c r="G197" s="60" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H197" s="63" t="n">
-        <v>0.252399596521761</v>
-      </c>
-      <c r="I197" s="63" t="n">
-        <v>0.7217579143506243</v>
-      </c>
-      <c r="J197" s="61" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="30" customHeight="1">
-      <c r="A198" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B198" s="56" t="inlineStr">
-        <is>
-          <t>POFP</t>
-        </is>
-      </c>
-      <c r="C198" s="57" t="inlineStr">
-        <is>
-          <t>3. Workshop</t>
-        </is>
-      </c>
-      <c r="D198" s="57" t="inlineStr">
-        <is>
-          <t>3. Workshop</t>
-        </is>
-      </c>
-      <c r="E198" s="57" t="inlineStr"/>
-      <c r="F198" s="58" t="n">
-        <v>2.2297697e-05</v>
-      </c>
-      <c r="G198" s="56" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H198" s="59" t="n">
-        <v>0.1030495225818688</v>
-      </c>
-      <c r="I198" s="59" t="n">
-        <v>0.8248074369324931</v>
-      </c>
-      <c r="J198" s="57" t="inlineStr">
-        <is>
-          <t>184</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17743,7 @@
       </c>
       <c r="B199" s="60" t="inlineStr">
         <is>
-          <t>ABF</t>
+          <t>POFP</t>
         </is>
       </c>
       <c r="C199" s="61" t="inlineStr">
@@ -17745,109 +17753,109 @@
       </c>
       <c r="D199" s="61" t="inlineStr">
         <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E199" s="61" t="inlineStr"/>
       <c r="F199" s="62" t="n">
+        <v>5.4613836e-05</v>
+      </c>
+      <c r="G199" s="60" t="inlineStr">
+        <is>
+          <t>kg C2H4 eq</t>
+        </is>
+      </c>
+      <c r="H199" s="63" t="n">
+        <v>0.252399596521761</v>
+      </c>
+      <c r="I199" s="63" t="n">
+        <v>0.7217579143506243</v>
+      </c>
+      <c r="J199" s="61" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B200" s="56" t="inlineStr">
+        <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="C200" s="57" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="D200" s="57" t="inlineStr">
+        <is>
+          <t>3. Workshop</t>
+        </is>
+      </c>
+      <c r="E200" s="57" t="inlineStr"/>
+      <c r="F200" s="58" t="n">
+        <v>2.2297697e-05</v>
+      </c>
+      <c r="G200" s="56" t="inlineStr">
+        <is>
+          <t>kg C2H4 eq</t>
+        </is>
+      </c>
+      <c r="H200" s="59" t="n">
+        <v>0.1030495225818688</v>
+      </c>
+      <c r="I200" s="59" t="n">
+        <v>0.8248074369324931</v>
+      </c>
+      <c r="J200" s="57" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="60" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B201" s="60" t="inlineStr">
+        <is>
+          <t>ABF</t>
+        </is>
+      </c>
+      <c r="C201" s="61" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D201" s="61" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E201" s="61" t="inlineStr"/>
+      <c r="F201" s="62" t="n">
         <v>2.1720667</v>
       </c>
-      <c r="G199" s="60" t="inlineStr">
+      <c r="G201" s="60" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H199" s="63" t="n">
+      <c r="H201" s="63" t="n">
         <v>0.7011506749449401</v>
       </c>
-      <c r="I199" s="63" t="n">
+      <c r="I201" s="63" t="n">
         <v>0.7011506749449401</v>
       </c>
-      <c r="J199" s="61" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="30" customHeight="1">
-      <c r="A200" s="64" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B200" s="64" t="inlineStr">
-        <is>
-          <t>ABF</t>
-        </is>
-      </c>
-      <c r="C200" s="65" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D200" s="65" t="inlineStr">
-        <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E200" s="65" t="inlineStr"/>
-      <c r="F200" s="66" t="n">
-        <v>0.26664609</v>
-      </c>
-      <c r="G200" s="64" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H200" s="67" t="n">
-        <v>0.0860742839871949</v>
-      </c>
-      <c r="I200" s="67" t="n">
-        <v>0.787224958932135</v>
-      </c>
-      <c r="J200" s="65" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="30" customHeight="1">
-      <c r="A201" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B201" s="56" t="inlineStr">
-        <is>
-          <t>ABF</t>
-        </is>
-      </c>
-      <c r="C201" s="57" t="inlineStr">
-        <is>
-          <t>2. Wastewater Treatment Plant</t>
-        </is>
-      </c>
-      <c r="D201" s="57" t="inlineStr">
-        <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E201" s="57" t="inlineStr"/>
-      <c r="F201" s="58" t="n">
-        <v>0.1843259</v>
-      </c>
-      <c r="G201" s="56" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H201" s="59" t="n">
-        <v>0.059501040734538</v>
-      </c>
-      <c r="I201" s="59" t="n">
-        <v>0.8467259996666729</v>
-      </c>
-      <c r="J201" s="57" t="inlineStr">
+      <c r="J201" s="61" t="inlineStr">
         <is>
           <t>264</t>
         </is>
@@ -17861,79 +17869,79 @@
       </c>
       <c r="B202" s="64" t="inlineStr">
         <is>
-          <t>ABN</t>
+          <t>ABF</t>
         </is>
       </c>
       <c r="C202" s="65" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D202" s="65" t="inlineStr">
         <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
       <c r="E202" s="65" t="inlineStr"/>
       <c r="F202" s="66" t="n">
-        <v>2.4812594e-07</v>
+        <v>0.26664609</v>
       </c>
       <c r="G202" s="64" t="inlineStr">
         <is>
-          <t>kg Sb eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H202" s="67" t="n">
-        <v>0.5937604573234</v>
+        <v>0.0860742839871949</v>
       </c>
       <c r="I202" s="67" t="n">
-        <v>0.5937604573234</v>
+        <v>0.787224958932135</v>
       </c>
       <c r="J202" s="65" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>265</t>
         </is>
       </c>
     </row>
     <row r="203" ht="30" customHeight="1">
-      <c r="A203" s="60" t="inlineStr">
+      <c r="A203" s="56" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B203" s="60" t="inlineStr">
-        <is>
-          <t>ABN</t>
-        </is>
-      </c>
-      <c r="C203" s="61" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D203" s="61" t="inlineStr">
-        <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E203" s="61" t="inlineStr"/>
-      <c r="F203" s="62" t="n">
-        <v>6.2463978e-08</v>
-      </c>
-      <c r="G203" s="60" t="inlineStr">
-        <is>
-          <t>kg Sb eq</t>
-        </is>
-      </c>
-      <c r="H203" s="63" t="n">
-        <v>0.1494750615091626</v>
-      </c>
-      <c r="I203" s="63" t="n">
-        <v>0.7432355188325626</v>
-      </c>
-      <c r="J203" s="61" t="inlineStr">
-        <is>
-          <t>224</t>
+      <c r="B203" s="56" t="inlineStr">
+        <is>
+          <t>ABF</t>
+        </is>
+      </c>
+      <c r="C203" s="57" t="inlineStr">
+        <is>
+          <t>2. Wastewater Treatment Plant</t>
+        </is>
+      </c>
+      <c r="D203" s="57" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E203" s="57" t="inlineStr"/>
+      <c r="F203" s="58" t="n">
+        <v>0.1843259</v>
+      </c>
+      <c r="G203" s="56" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H203" s="59" t="n">
+        <v>0.059501040734538</v>
+      </c>
+      <c r="I203" s="59" t="n">
+        <v>0.8467259996666729</v>
+      </c>
+      <c r="J203" s="57" t="inlineStr">
+        <is>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -17955,12 +17963,12 @@
       </c>
       <c r="D204" s="65" t="inlineStr">
         <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E204" s="65" t="inlineStr"/>
       <c r="F204" s="66" t="n">
-        <v>2.1559153e-08</v>
+        <v>2.4812594e-07</v>
       </c>
       <c r="G204" s="64" t="inlineStr">
         <is>
@@ -17968,56 +17976,56 @@
         </is>
       </c>
       <c r="H204" s="67" t="n">
-        <v>0.05159062589258161</v>
+        <v>0.5937604573234</v>
       </c>
       <c r="I204" s="67" t="n">
-        <v>0.7948261447251441</v>
+        <v>0.5937604573234</v>
       </c>
       <c r="J204" s="65" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="205" ht="30" customHeight="1">
-      <c r="A205" s="56" t="inlineStr">
+      <c r="A205" s="60" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B205" s="56" t="inlineStr">
+      <c r="B205" s="60" t="inlineStr">
         <is>
           <t>ABN</t>
         </is>
       </c>
-      <c r="C205" s="57" t="inlineStr">
-        <is>
-          <t>7. Hazardous Waste Treatment System</t>
-        </is>
-      </c>
-      <c r="D205" s="57" t="inlineStr">
-        <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E205" s="57" t="inlineStr"/>
-      <c r="F205" s="58" t="n">
-        <v>2.1072143e-08</v>
-      </c>
-      <c r="G205" s="56" t="inlineStr">
+      <c r="C205" s="61" t="inlineStr">
+        <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D205" s="61" t="inlineStr">
+        <is>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E205" s="61" t="inlineStr"/>
+      <c r="F205" s="62" t="n">
+        <v>6.2463978e-08</v>
+      </c>
+      <c r="G205" s="60" t="inlineStr">
         <is>
           <t>kg Sb eq</t>
         </is>
       </c>
-      <c r="H205" s="59" t="n">
-        <v>0.05042522061362904</v>
-      </c>
-      <c r="I205" s="59" t="n">
-        <v>0.8452513653387732</v>
-      </c>
-      <c r="J205" s="57" t="inlineStr">
-        <is>
-          <t>226</t>
+      <c r="H205" s="63" t="n">
+        <v>0.1494750615091626</v>
+      </c>
+      <c r="I205" s="63" t="n">
+        <v>0.7432355188325626</v>
+      </c>
+      <c r="J205" s="61" t="inlineStr">
+        <is>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -18029,121 +18037,121 @@
       </c>
       <c r="B206" s="64" t="inlineStr">
         <is>
-          <t>ETP Terrestrial</t>
+          <t>ABN</t>
         </is>
       </c>
       <c r="C206" s="65" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D206" s="65" t="inlineStr">
         <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E206" s="65" t="inlineStr"/>
       <c r="F206" s="66" t="n">
+        <v>2.1559153e-08</v>
+      </c>
+      <c r="G206" s="64" t="inlineStr">
+        <is>
+          <t>kg Sb eq</t>
+        </is>
+      </c>
+      <c r="H206" s="67" t="n">
+        <v>0.05159062589258161</v>
+      </c>
+      <c r="I206" s="67" t="n">
+        <v>0.7948261447251441</v>
+      </c>
+      <c r="J206" s="65" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B207" s="56" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="C207" s="57" t="inlineStr">
+        <is>
+          <t>7. Hazardous Waste Treatment System</t>
+        </is>
+      </c>
+      <c r="D207" s="57" t="inlineStr">
+        <is>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E207" s="57" t="inlineStr"/>
+      <c r="F207" s="58" t="n">
+        <v>2.1072143e-08</v>
+      </c>
+      <c r="G207" s="56" t="inlineStr">
+        <is>
+          <t>kg Sb eq</t>
+        </is>
+      </c>
+      <c r="H207" s="59" t="n">
+        <v>0.05042522061362904</v>
+      </c>
+      <c r="I207" s="59" t="n">
+        <v>0.8452513653387732</v>
+      </c>
+      <c r="J207" s="57" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="64" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B208" s="64" t="inlineStr">
+        <is>
+          <t>ETP Terrestrial</t>
+        </is>
+      </c>
+      <c r="C208" s="65" t="inlineStr">
+        <is>
+          <t>5. Hazardous Waste Transportation</t>
+        </is>
+      </c>
+      <c r="D208" s="65" t="inlineStr">
+        <is>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E208" s="65" t="inlineStr"/>
+      <c r="F208" s="66" t="n">
         <v>0.31389255</v>
       </c>
-      <c r="G206" s="64" t="inlineStr">
+      <c r="G208" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H206" s="67" t="n">
+      <c r="H208" s="67" t="n">
         <v>0.5920839086749915</v>
       </c>
-      <c r="I206" s="67" t="n">
+      <c r="I208" s="67" t="n">
         <v>0.5920839086749915</v>
       </c>
-      <c r="J206" s="65" t="inlineStr">
+      <c r="J208" s="65" t="inlineStr">
         <is>
           <t>305</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="60" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B207" s="60" t="inlineStr">
-        <is>
-          <t>ETP Terrestrial</t>
-        </is>
-      </c>
-      <c r="C207" s="61" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D207" s="61" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E207" s="61" t="inlineStr"/>
-      <c r="F207" s="62" t="n">
-        <v>0.085753554</v>
-      </c>
-      <c r="G207" s="60" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H207" s="63" t="n">
-        <v>0.1617537575679702</v>
-      </c>
-      <c r="I207" s="63" t="n">
-        <v>0.7538376662429617</v>
-      </c>
-      <c r="J207" s="61" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B208" s="56" t="inlineStr">
-        <is>
-          <t>ETP Terrestrial</t>
-        </is>
-      </c>
-      <c r="C208" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D208" s="57" t="inlineStr">
-        <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E208" s="57" t="inlineStr"/>
-      <c r="F208" s="58" t="n">
-        <v>0.065601664</v>
-      </c>
-      <c r="G208" s="56" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H208" s="59" t="n">
-        <v>0.1237419927191757</v>
-      </c>
-      <c r="I208" s="59" t="n">
-        <v>0.8775796589621373</v>
-      </c>
-      <c r="J208" s="57" t="inlineStr">
-        <is>
-          <t>307</t>
         </is>
       </c>
     </row>
@@ -18155,121 +18163,121 @@
       </c>
       <c r="B209" s="60" t="inlineStr">
         <is>
-          <t>ETP Freshwater</t>
+          <t>ETP Terrestrial</t>
         </is>
       </c>
       <c r="C209" s="61" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D209" s="61" t="inlineStr">
         <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E209" s="61" t="inlineStr"/>
       <c r="F209" s="62" t="n">
+        <v>0.085753554</v>
+      </c>
+      <c r="G209" s="60" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H209" s="63" t="n">
+        <v>0.1617537575679702</v>
+      </c>
+      <c r="I209" s="63" t="n">
+        <v>0.7538376662429617</v>
+      </c>
+      <c r="J209" s="61" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B210" s="56" t="inlineStr">
+        <is>
+          <t>ETP Terrestrial</t>
+        </is>
+      </c>
+      <c r="C210" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D210" s="57" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E210" s="57" t="inlineStr"/>
+      <c r="F210" s="58" t="n">
+        <v>0.065601664</v>
+      </c>
+      <c r="G210" s="56" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H210" s="59" t="n">
+        <v>0.1237419927191757</v>
+      </c>
+      <c r="I210" s="59" t="n">
+        <v>0.8775796589621373</v>
+      </c>
+      <c r="J210" s="57" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="30" customHeight="1">
+      <c r="A211" s="60" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B211" s="60" t="inlineStr">
+        <is>
+          <t>ETP Freshwater</t>
+        </is>
+      </c>
+      <c r="C211" s="61" t="inlineStr">
+        <is>
+          <t>7. Hazardous Waste Treatment System</t>
+        </is>
+      </c>
+      <c r="D211" s="61" t="inlineStr">
+        <is>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E211" s="61" t="inlineStr"/>
+      <c r="F211" s="62" t="n">
         <v>0.00031518542</v>
       </c>
-      <c r="G209" s="60" t="inlineStr">
+      <c r="G211" s="60" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H209" s="63" t="n">
+      <c r="H211" s="63" t="n">
         <v>0.513818099554873</v>
       </c>
-      <c r="I209" s="63" t="n">
+      <c r="I211" s="63" t="n">
         <v>0.513818099554873</v>
       </c>
-      <c r="J209" s="61" t="inlineStr">
+      <c r="J211" s="61" t="inlineStr">
         <is>
           <t>346</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="30" customHeight="1">
-      <c r="A210" s="64" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B210" s="64" t="inlineStr">
-        <is>
-          <t>ETP Freshwater</t>
-        </is>
-      </c>
-      <c r="C210" s="65" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D210" s="65" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E210" s="65" t="inlineStr"/>
-      <c r="F210" s="66" t="n">
-        <v>0.00014912397</v>
-      </c>
-      <c r="G210" s="64" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H210" s="67" t="n">
-        <v>0.2431032338471681</v>
-      </c>
-      <c r="I210" s="67" t="n">
-        <v>0.7569213334020412</v>
-      </c>
-      <c r="J210" s="65" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="30" customHeight="1">
-      <c r="A211" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B211" s="56" t="inlineStr">
-        <is>
-          <t>ETP Freshwater</t>
-        </is>
-      </c>
-      <c r="C211" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D211" s="57" t="inlineStr">
-        <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E211" s="57" t="inlineStr"/>
-      <c r="F211" s="58" t="n">
-        <v>5.0562969e-05</v>
-      </c>
-      <c r="G211" s="56" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H211" s="59" t="n">
-        <v>0.08242820571913498</v>
-      </c>
-      <c r="I211" s="59" t="n">
-        <v>0.8393495391211762</v>
-      </c>
-      <c r="J211" s="57" t="inlineStr">
-        <is>
-          <t>348</t>
         </is>
       </c>
     </row>
@@ -18281,121 +18289,121 @@
       </c>
       <c r="B212" s="64" t="inlineStr">
         <is>
-          <t>ETP Marine</t>
+          <t>ETP Freshwater</t>
         </is>
       </c>
       <c r="C212" s="65" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D212" s="65" t="inlineStr">
         <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E212" s="65" t="inlineStr"/>
       <c r="F212" s="66" t="n">
+        <v>0.00014912397</v>
+      </c>
+      <c r="G212" s="64" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H212" s="67" t="n">
+        <v>0.2431032338471681</v>
+      </c>
+      <c r="I212" s="67" t="n">
+        <v>0.7569213334020412</v>
+      </c>
+      <c r="J212" s="65" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="30" customHeight="1">
+      <c r="A213" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B213" s="56" t="inlineStr">
+        <is>
+          <t>ETP Freshwater</t>
+        </is>
+      </c>
+      <c r="C213" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D213" s="57" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E213" s="57" t="inlineStr"/>
+      <c r="F213" s="58" t="n">
+        <v>5.0562969e-05</v>
+      </c>
+      <c r="G213" s="56" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H213" s="59" t="n">
+        <v>0.08242820571913498</v>
+      </c>
+      <c r="I213" s="59" t="n">
+        <v>0.8393495391211762</v>
+      </c>
+      <c r="J213" s="57" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="64" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B214" s="64" t="inlineStr">
+        <is>
+          <t>ETP Marine</t>
+        </is>
+      </c>
+      <c r="C214" s="65" t="inlineStr">
+        <is>
+          <t>7. Hazardous Waste Treatment System</t>
+        </is>
+      </c>
+      <c r="D214" s="65" t="inlineStr">
+        <is>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E214" s="65" t="inlineStr"/>
+      <c r="F214" s="66" t="n">
         <v>0.00044327538</v>
       </c>
-      <c r="G212" s="64" t="inlineStr">
+      <c r="G214" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H212" s="67" t="n">
+      <c r="H214" s="67" t="n">
         <v>0.4286394847917845</v>
       </c>
-      <c r="I212" s="67" t="n">
+      <c r="I214" s="67" t="n">
         <v>0.4286394847917845</v>
       </c>
-      <c r="J212" s="65" t="inlineStr">
+      <c r="J214" s="65" t="inlineStr">
         <is>
           <t>387</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="30" customHeight="1">
-      <c r="A213" s="60" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B213" s="60" t="inlineStr">
-        <is>
-          <t>ETP Marine</t>
-        </is>
-      </c>
-      <c r="C213" s="61" t="inlineStr">
-        <is>
-          <t>5. Hazardous Waste Transportation</t>
-        </is>
-      </c>
-      <c r="D213" s="61" t="inlineStr">
-        <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E213" s="61" t="inlineStr"/>
-      <c r="F213" s="62" t="n">
-        <v>0.00023537939</v>
-      </c>
-      <c r="G213" s="60" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H213" s="63" t="n">
-        <v>0.2276077242553027</v>
-      </c>
-      <c r="I213" s="63" t="n">
-        <v>0.6562472090470872</v>
-      </c>
-      <c r="J213" s="61" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="30" customHeight="1">
-      <c r="A214" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B214" s="56" t="inlineStr">
-        <is>
-          <t>ETP Marine</t>
-        </is>
-      </c>
-      <c r="C214" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D214" s="57" t="inlineStr">
-        <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E214" s="57" t="inlineStr"/>
-      <c r="F214" s="58" t="n">
-        <v>0.00016791294</v>
-      </c>
-      <c r="G214" s="56" t="inlineStr">
-        <is>
-          <t>kg 1,4-DCB</t>
-        </is>
-      </c>
-      <c r="H214" s="59" t="n">
-        <v>0.1623688554312983</v>
-      </c>
-      <c r="I214" s="59" t="n">
-        <v>0.8186160644783855</v>
-      </c>
-      <c r="J214" s="57" t="inlineStr">
-        <is>
-          <t>389</t>
         </is>
       </c>
     </row>
@@ -18407,22 +18415,22 @@
       </c>
       <c r="B215" s="60" t="inlineStr">
         <is>
-          <t>HTC</t>
+          <t>ETP Marine</t>
         </is>
       </c>
       <c r="C215" s="61" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D215" s="61" t="inlineStr">
         <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
       <c r="E215" s="61" t="inlineStr"/>
       <c r="F215" s="62" t="n">
-        <v>0.00079684878</v>
+        <v>0.00023537939</v>
       </c>
       <c r="G215" s="60" t="inlineStr">
         <is>
@@ -18430,56 +18438,56 @@
         </is>
       </c>
       <c r="H215" s="63" t="n">
-        <v>0.4807201746413189</v>
+        <v>0.2276077242553027</v>
       </c>
       <c r="I215" s="63" t="n">
-        <v>0.4807201746413189</v>
+        <v>0.6562472090470872</v>
       </c>
       <c r="J215" s="61" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>388</t>
         </is>
       </c>
     </row>
     <row r="216" ht="30" customHeight="1">
-      <c r="A216" s="64" t="inlineStr">
+      <c r="A216" s="56" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B216" s="64" t="inlineStr">
-        <is>
-          <t>HTC</t>
-        </is>
-      </c>
-      <c r="C216" s="65" t="inlineStr">
+      <c r="B216" s="56" t="inlineStr">
+        <is>
+          <t>ETP Marine</t>
+        </is>
+      </c>
+      <c r="C216" s="57" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D216" s="65" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E216" s="65" t="inlineStr"/>
-      <c r="F216" s="66" t="n">
-        <v>0.00031633648</v>
-      </c>
-      <c r="G216" s="64" t="inlineStr">
+      <c r="D216" s="57" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E216" s="57" t="inlineStr"/>
+      <c r="F216" s="58" t="n">
+        <v>0.00016791294</v>
+      </c>
+      <c r="G216" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H216" s="67" t="n">
-        <v>0.1908383770268433</v>
-      </c>
-      <c r="I216" s="67" t="n">
-        <v>0.6715585516681623</v>
-      </c>
-      <c r="J216" s="65" t="inlineStr">
-        <is>
-          <t>429</t>
+      <c r="H216" s="59" t="n">
+        <v>0.1623688554312983</v>
+      </c>
+      <c r="I216" s="59" t="n">
+        <v>0.8186160644783855</v>
+      </c>
+      <c r="J216" s="57" t="inlineStr">
+        <is>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -18496,17 +18504,17 @@
       </c>
       <c r="C217" s="61" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>7. Hazardous Waste Treatment System</t>
         </is>
       </c>
       <c r="D217" s="61" t="inlineStr">
         <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
         </is>
       </c>
       <c r="E217" s="61" t="inlineStr"/>
       <c r="F217" s="62" t="n">
-        <v>0.00017929279</v>
+        <v>0.00079684878</v>
       </c>
       <c r="G217" s="60" t="inlineStr">
         <is>
@@ -18514,56 +18522,56 @@
         </is>
       </c>
       <c r="H217" s="63" t="n">
-        <v>0.108163133939578</v>
+        <v>0.4807201746413189</v>
       </c>
       <c r="I217" s="63" t="n">
-        <v>0.7797216856077402</v>
+        <v>0.4807201746413189</v>
       </c>
       <c r="J217" s="61" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>428</t>
         </is>
       </c>
     </row>
     <row r="218" ht="30" customHeight="1">
-      <c r="A218" s="56" t="inlineStr">
+      <c r="A218" s="64" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B218" s="56" t="inlineStr">
+      <c r="B218" s="64" t="inlineStr">
         <is>
           <t>HTC</t>
         </is>
       </c>
-      <c r="C218" s="57" t="inlineStr">
+      <c r="C218" s="65" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D218" s="57" t="inlineStr">
-        <is>
-          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E218" s="57" t="inlineStr"/>
-      <c r="F218" s="58" t="n">
-        <v>0.00017485713</v>
-      </c>
-      <c r="G218" s="56" t="inlineStr">
+      <c r="D218" s="65" t="inlineStr">
+        <is>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E218" s="65" t="inlineStr"/>
+      <c r="F218" s="66" t="n">
+        <v>0.00031633648</v>
+      </c>
+      <c r="G218" s="64" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H218" s="59" t="n">
-        <v>0.1054872043236106</v>
-      </c>
-      <c r="I218" s="59" t="n">
-        <v>0.8852088899313508</v>
-      </c>
-      <c r="J218" s="57" t="inlineStr">
-        <is>
-          <t>430</t>
+      <c r="H218" s="67" t="n">
+        <v>0.1908383770268433</v>
+      </c>
+      <c r="I218" s="67" t="n">
+        <v>0.6715585516681623</v>
+      </c>
+      <c r="J218" s="65" t="inlineStr">
+        <is>
+          <t>429</t>
         </is>
       </c>
     </row>
@@ -18575,22 +18583,22 @@
       </c>
       <c r="B219" s="60" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>HTC</t>
         </is>
       </c>
       <c r="C219" s="61" t="inlineStr">
         <is>
-          <t>7. Hazardous Waste Treatment System</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D219" s="61" t="inlineStr">
         <is>
-          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
       <c r="E219" s="61" t="inlineStr"/>
       <c r="F219" s="62" t="n">
-        <v>0.0216115</v>
+        <v>0.00017929279</v>
       </c>
       <c r="G219" s="60" t="inlineStr">
         <is>
@@ -18598,14 +18606,14 @@
         </is>
       </c>
       <c r="H219" s="63" t="n">
-        <v>0.7720221998312029</v>
+        <v>0.108163133939578</v>
       </c>
       <c r="I219" s="63" t="n">
-        <v>0.7720221998312029</v>
+        <v>0.7797216856077402</v>
       </c>
       <c r="J219" s="61" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>431</t>
         </is>
       </c>
     </row>
@@ -18617,22 +18625,22 @@
       </c>
       <c r="B220" s="56" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>HTC</t>
         </is>
       </c>
       <c r="C220" s="57" t="inlineStr">
         <is>
-          <t>5. Hazardous Waste Transportation</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D220" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E220" s="57" t="inlineStr"/>
       <c r="F220" s="58" t="n">
-        <v>0.0055755844</v>
+        <v>0.00017485713</v>
       </c>
       <c r="G220" s="56" t="inlineStr">
         <is>
@@ -18640,56 +18648,56 @@
         </is>
       </c>
       <c r="H220" s="59" t="n">
-        <v>0.1991752045824</v>
+        <v>0.1054872043236106</v>
       </c>
       <c r="I220" s="59" t="n">
-        <v>0.9711974044136029</v>
+        <v>0.8852088899313508</v>
       </c>
       <c r="J220" s="57" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>430</t>
         </is>
       </c>
     </row>
     <row r="221" ht="30" customHeight="1">
-      <c r="A221" s="56" t="inlineStr">
+      <c r="A221" s="60" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B221" s="56" t="inlineStr">
-        <is>
-          <t>WSF</t>
-        </is>
-      </c>
-      <c r="C221" s="57" t="inlineStr">
-        <is>
-          <t>2. Wastewater Treatment Plant</t>
-        </is>
-      </c>
-      <c r="D221" s="57" t="inlineStr">
-        <is>
-          <t>2. Wastewater Treatment Plant</t>
-        </is>
-      </c>
-      <c r="E221" s="57" t="inlineStr"/>
-      <c r="F221" s="58" t="n">
-        <v>-32.117591</v>
-      </c>
-      <c r="G221" s="56" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="H221" s="59" t="n">
-        <v>-1.001042165550009</v>
-      </c>
-      <c r="I221" s="59" t="n">
-        <v>1.001042165550009</v>
-      </c>
-      <c r="J221" s="57" t="inlineStr">
-        <is>
-          <t>568</t>
+      <c r="B221" s="60" t="inlineStr">
+        <is>
+          <t>HTN</t>
+        </is>
+      </c>
+      <c r="C221" s="61" t="inlineStr">
+        <is>
+          <t>7. Hazardous Waste Treatment System</t>
+        </is>
+      </c>
+      <c r="D221" s="61" t="inlineStr">
+        <is>
+          <t>Waste mineral oil {RoW}| treatment of, hazardous waste incineration | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E221" s="61" t="inlineStr"/>
+      <c r="F221" s="62" t="n">
+        <v>0.0216115</v>
+      </c>
+      <c r="G221" s="60" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H221" s="63" t="n">
+        <v>0.7720221998312029</v>
+      </c>
+      <c r="I221" s="63" t="n">
+        <v>0.7720221998312029</v>
+      </c>
+      <c r="J221" s="61" t="inlineStr">
+        <is>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -18701,289 +18709,289 @@
       </c>
       <c r="B222" s="56" t="inlineStr">
         <is>
-          <t>LUC</t>
+          <t>HTN</t>
         </is>
       </c>
       <c r="C222" s="57" t="inlineStr">
         <is>
-          <t>4. Mining Utility</t>
+          <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
       <c r="D222" s="57" t="inlineStr">
         <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+          <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
       <c r="E222" s="57" t="inlineStr"/>
       <c r="F222" s="58" t="n">
+        <v>0.0055755844</v>
+      </c>
+      <c r="G222" s="56" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H222" s="59" t="n">
+        <v>0.1991752045824</v>
+      </c>
+      <c r="I222" s="59" t="n">
+        <v>0.9711974044136029</v>
+      </c>
+      <c r="J222" s="57" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B223" s="56" t="inlineStr">
+        <is>
+          <t>WSF</t>
+        </is>
+      </c>
+      <c r="C223" s="57" t="inlineStr">
+        <is>
+          <t>2. Wastewater Treatment Plant</t>
+        </is>
+      </c>
+      <c r="D223" s="57" t="inlineStr">
+        <is>
+          <t>2. Wastewater Treatment Plant</t>
+        </is>
+      </c>
+      <c r="E223" s="57" t="inlineStr"/>
+      <c r="F223" s="58" t="n">
+        <v>-32.117591</v>
+      </c>
+      <c r="G223" s="56" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H223" s="59" t="n">
+        <v>-1.001042165550009</v>
+      </c>
+      <c r="I223" s="59" t="n">
+        <v>1.001042165550009</v>
+      </c>
+      <c r="J223" s="57" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="56" t="inlineStr">
+        <is>
+          <t>PROC UT LMO</t>
+        </is>
+      </c>
+      <c r="B224" s="56" t="inlineStr">
+        <is>
+          <t>LUC</t>
+        </is>
+      </c>
+      <c r="C224" s="57" t="inlineStr">
+        <is>
+          <t>4. Mining Utility</t>
+        </is>
+      </c>
+      <c r="D224" s="57" t="inlineStr">
+        <is>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E224" s="57" t="inlineStr"/>
+      <c r="F224" s="58" t="n">
         <v>0.053601813</v>
       </c>
-      <c r="G222" s="56" t="inlineStr">
+      <c r="G224" s="56" t="inlineStr">
         <is>
           <t>m2a crop eq</t>
         </is>
       </c>
-      <c r="H222" s="59" t="n">
+      <c r="H224" s="59" t="n">
         <v>0.8291484999439803</v>
       </c>
-      <c r="I222" s="59" t="n">
+      <c r="I224" s="59" t="n">
         <v>0.8291484999439803</v>
       </c>
-      <c r="J222" s="57" t="inlineStr">
+      <c r="J224" s="57" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="30" customHeight="1">
-      <c r="A223" s="60" t="inlineStr">
+    <row r="225" ht="30" customHeight="1">
+      <c r="A225" s="60" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B223" s="60" t="inlineStr">
+      <c r="B225" s="60" t="inlineStr">
         <is>
           <t>CEN</t>
         </is>
       </c>
-      <c r="C223" s="61" t="inlineStr">
+      <c r="C225" s="61" t="inlineStr">
         <is>
           <t>4. Mining Utility</t>
         </is>
       </c>
-      <c r="D223" s="61" t="inlineStr">
+      <c r="D225" s="61" t="inlineStr">
         <is>
           <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
-      <c r="E223" s="61" t="inlineStr"/>
-      <c r="F223" s="62" t="n">
+      <c r="E225" s="61" t="inlineStr"/>
+      <c r="F225" s="62" t="n">
         <v>2.3109399865612</v>
       </c>
-      <c r="G223" s="60" t="inlineStr">
+      <c r="G225" s="60" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H223" s="63" t="n">
+      <c r="H225" s="63" t="n">
         <v>0.6769932782032658</v>
       </c>
-      <c r="I223" s="63" t="n">
+      <c r="I225" s="63" t="n">
         <v>0.6769932782032658</v>
       </c>
-      <c r="J223" s="61" t="inlineStr">
+      <c r="J225" s="61" t="inlineStr">
         <is>
           <t>592, 633, 676</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="30" customHeight="1">
-      <c r="A224" s="64" t="inlineStr">
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="64" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B224" s="64" t="inlineStr">
+      <c r="B226" s="64" t="inlineStr">
         <is>
           <t>CEN</t>
         </is>
       </c>
-      <c r="C224" s="65" t="inlineStr">
+      <c r="C226" s="65" t="inlineStr">
         <is>
           <t>5. Hazardous Waste Transportation</t>
         </is>
       </c>
-      <c r="D224" s="65" t="inlineStr">
+      <c r="D226" s="65" t="inlineStr">
         <is>
           <t>Transport, freight, lorry 16-32 metric ton, euro4 {RoW}| market for transport, freight, lorry 16-32 metric ton, EURO4 | Cut-off, S</t>
         </is>
       </c>
-      <c r="E224" s="65" t="inlineStr"/>
-      <c r="F224" s="66" t="n">
+      <c r="E226" s="65" t="inlineStr"/>
+      <c r="F226" s="66" t="n">
         <v>0.286647279917</v>
       </c>
-      <c r="G224" s="64" t="inlineStr">
+      <c r="G226" s="64" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H224" s="67" t="n">
+      <c r="H226" s="67" t="n">
         <v>0.0839737435188994</v>
       </c>
-      <c r="I224" s="67" t="n">
+      <c r="I226" s="67" t="n">
         <v>0.7609670217221652</v>
       </c>
-      <c r="J224" s="65" t="inlineStr">
+      <c r="J226" s="65" t="inlineStr">
         <is>
           <t>593, 635, 675</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="30" customHeight="1">
-      <c r="A225" s="56" t="inlineStr">
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="56" t="inlineStr">
         <is>
           <t>PROC UT LMO</t>
         </is>
       </c>
-      <c r="B225" s="56" t="inlineStr">
+      <c r="B227" s="56" t="inlineStr">
         <is>
           <t>CEN</t>
         </is>
       </c>
-      <c r="C225" s="57" t="inlineStr">
+      <c r="C227" s="57" t="inlineStr">
         <is>
           <t>2. Wastewater Treatment Plant</t>
         </is>
       </c>
-      <c r="D225" s="57" t="inlineStr">
+      <c r="D227" s="57" t="inlineStr">
         <is>
           <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
         </is>
       </c>
-      <c r="E225" s="57" t="inlineStr"/>
-      <c r="F225" s="58" t="n">
+      <c r="E227" s="57" t="inlineStr"/>
+      <c r="F227" s="58" t="n">
         <v>0.19611095571596</v>
       </c>
-      <c r="G225" s="56" t="inlineStr">
+      <c r="G227" s="56" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H225" s="59" t="n">
+      <c r="H227" s="59" t="n">
         <v>0.05745099378339363</v>
       </c>
-      <c r="I225" s="59" t="n">
+      <c r="I227" s="59" t="n">
         <v>0.8184180155055589</v>
       </c>
-      <c r="J225" s="57" t="inlineStr">
+      <c r="J227" s="57" t="inlineStr">
         <is>
           <t>592, 633, 676</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="30" customHeight="1">
-      <c r="A226" s="56" t="inlineStr">
-        <is>
-          <t>PROC UT LMO</t>
-        </is>
-      </c>
-      <c r="B226" s="56" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="C226" s="57" t="inlineStr">
-        <is>
-          <t>4. Mining Utility</t>
-        </is>
-      </c>
-      <c r="D226" s="57" t="inlineStr">
-        <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E226" s="57" t="inlineStr"/>
-      <c r="F226" s="58" t="n">
-        <v>1.96879528686</v>
-      </c>
-      <c r="G226" s="56" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="H226" s="59" t="n">
-        <v>0.8733664630206504</v>
-      </c>
-      <c r="I226" s="59" t="n">
-        <v>0.8733664630206504</v>
-      </c>
-      <c r="J226" s="57" t="inlineStr">
-        <is>
-          <t>715, 757, 798</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="30" customHeight="1">
-      <c r="A227" s="60" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B227" s="60" t="inlineStr">
-        <is>
-          <t>GWP</t>
-        </is>
-      </c>
-      <c r="C227" s="61" t="inlineStr">
-        <is>
-          <t>4. Boiler PLTU</t>
-        </is>
-      </c>
-      <c r="D227" s="61" t="inlineStr">
-        <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E227" s="61" t="inlineStr"/>
-      <c r="F227" s="62" t="n">
-        <v>0.019614931</v>
-      </c>
-      <c r="G227" s="60" t="inlineStr">
-        <is>
-          <t>kg CO2-eq</t>
-        </is>
-      </c>
-      <c r="H227" s="63" t="n">
-        <v>0.550191096359262</v>
-      </c>
-      <c r="I227" s="63" t="n">
-        <v>0.550191096359262</v>
-      </c>
-      <c r="J227" s="61" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="56" t="inlineStr">
         <is>
-          <t>PROC DOWN LMO</t>
+          <t>PROC UT LMO</t>
         </is>
       </c>
       <c r="B228" s="56" t="inlineStr">
         <is>
-          <t>GWP</t>
+          <t>CED</t>
         </is>
       </c>
       <c r="C228" s="57" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Mining Utility</t>
         </is>
       </c>
       <c r="D228" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
       <c r="E228" s="57" t="inlineStr"/>
       <c r="F228" s="58" t="n">
-        <v>0.0093778128</v>
+        <v>1.96879528686</v>
       </c>
       <c r="G228" s="56" t="inlineStr">
         <is>
-          <t>kg CO2-eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H228" s="59" t="n">
-        <v>0.2630439590067343</v>
+        <v>0.8733664630206504</v>
       </c>
       <c r="I228" s="59" t="n">
-        <v>0.8132350553659963</v>
+        <v>0.8733664630206504</v>
       </c>
       <c r="J228" s="57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>715, 757, 798</t>
         </is>
       </c>
     </row>
@@ -18995,37 +19003,37 @@
       </c>
       <c r="B229" s="60" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C229" s="61" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D229" s="61" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E229" s="61" t="inlineStr"/>
       <c r="F229" s="62" t="n">
-        <v>1.4693417e-09</v>
+        <v>0.019614931</v>
       </c>
       <c r="G229" s="60" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H229" s="63" t="n">
-        <v>0.6712972971787581</v>
+        <v>0.550191096359262</v>
       </c>
       <c r="I229" s="63" t="n">
-        <v>0.6712972971787581</v>
+        <v>0.550191096359262</v>
       </c>
       <c r="J229" s="61" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -19037,37 +19045,37 @@
       </c>
       <c r="B230" s="56" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>GWP</t>
         </is>
       </c>
       <c r="C230" s="57" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D230" s="57" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E230" s="57" t="inlineStr"/>
       <c r="F230" s="58" t="n">
-        <v>3.6889404e-10</v>
+        <v>0.0093778128</v>
       </c>
       <c r="G230" s="56" t="inlineStr">
         <is>
-          <t>kg CFC-11 eq</t>
+          <t>kg CO2-eq</t>
         </is>
       </c>
       <c r="H230" s="59" t="n">
-        <v>0.1685364078330811</v>
+        <v>0.2630439590067343</v>
       </c>
       <c r="I230" s="59" t="n">
-        <v>0.8398337050118392</v>
+        <v>0.8132350553659963</v>
       </c>
       <c r="J230" s="57" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -19079,37 +19087,37 @@
       </c>
       <c r="B231" s="60" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="C231" s="61" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D231" s="61" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E231" s="61" t="inlineStr"/>
       <c r="F231" s="62" t="n">
-        <v>0.00044221044</v>
+        <v>1.4693417e-09</v>
       </c>
       <c r="G231" s="60" t="inlineStr">
         <is>
-          <t>kg SO2 eq</t>
+          <t>kg CFC-11 eq</t>
         </is>
       </c>
       <c r="H231" s="63" t="n">
-        <v>0.5521445859474728</v>
+        <v>0.6712972971787581</v>
       </c>
       <c r="I231" s="63" t="n">
-        <v>0.5521445859474728</v>
+        <v>0.6712972971787581</v>
       </c>
       <c r="J231" s="61" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -19121,37 +19129,37 @@
       </c>
       <c r="B232" s="56" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="C232" s="57" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D232" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E232" s="57" t="inlineStr"/>
       <c r="F232" s="58" t="n">
-        <v>0.00022190635</v>
+        <v>3.6889404e-10</v>
       </c>
       <c r="G232" s="56" t="inlineStr">
         <is>
-          <t>kg SO2 eq</t>
+          <t>kg CFC-11 eq</t>
         </is>
       </c>
       <c r="H232" s="59" t="n">
-        <v>0.277072585034096</v>
+        <v>0.1685364078330811</v>
       </c>
       <c r="I232" s="59" t="n">
-        <v>0.8292171709815688</v>
+        <v>0.8398337050118392</v>
       </c>
       <c r="J232" s="57" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -19163,7 +19171,7 @@
       </c>
       <c r="B233" s="60" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C233" s="61" t="inlineStr">
@@ -19178,106 +19186,106 @@
       </c>
       <c r="E233" s="61" t="inlineStr"/>
       <c r="F233" s="62" t="n">
+        <v>0.00044221044</v>
+      </c>
+      <c r="G233" s="60" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H233" s="63" t="n">
+        <v>0.5521445859474728</v>
+      </c>
+      <c r="I233" s="63" t="n">
+        <v>0.5521445859474728</v>
+      </c>
+      <c r="J233" s="61" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="56" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B234" s="56" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C234" s="57" t="inlineStr">
+        <is>
+          <t>2. Coal Transport Export</t>
+        </is>
+      </c>
+      <c r="D234" s="57" t="inlineStr">
+        <is>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E234" s="57" t="inlineStr"/>
+      <c r="F234" s="58" t="n">
+        <v>0.00022190635</v>
+      </c>
+      <c r="G234" s="56" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="H234" s="59" t="n">
+        <v>0.277072585034096</v>
+      </c>
+      <c r="I234" s="59" t="n">
+        <v>0.8292171709815688</v>
+      </c>
+      <c r="J234" s="57" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="60" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B235" s="60" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C235" s="61" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="D235" s="61" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="E235" s="61" t="inlineStr"/>
+      <c r="F235" s="62" t="n">
         <v>4.8994289e-05</v>
       </c>
-      <c r="G233" s="60" t="inlineStr">
+      <c r="G235" s="60" t="inlineStr">
         <is>
           <t>kg PO4--- eq</t>
         </is>
       </c>
-      <c r="H233" s="63" t="n">
+      <c r="H235" s="63" t="n">
         <v>0.5075059505016913</v>
       </c>
-      <c r="I233" s="63" t="n">
+      <c r="I235" s="63" t="n">
         <v>0.5075059505016913</v>
       </c>
-      <c r="J233" s="61" t="inlineStr">
+      <c r="J235" s="61" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="30" customHeight="1">
-      <c r="A234" s="64" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B234" s="64" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C234" s="65" t="inlineStr">
-        <is>
-          <t>2. Coal Transport Export</t>
-        </is>
-      </c>
-      <c r="D234" s="65" t="inlineStr">
-        <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E234" s="65" t="inlineStr"/>
-      <c r="F234" s="66" t="n">
-        <v>2.1783575e-05</v>
-      </c>
-      <c r="G234" s="64" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H234" s="67" t="n">
-        <v>0.2256445426874116</v>
-      </c>
-      <c r="I234" s="67" t="n">
-        <v>0.733150493189103</v>
-      </c>
-      <c r="J234" s="65" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="30" customHeight="1">
-      <c r="A235" s="56" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B235" s="56" t="inlineStr">
-        <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="C235" s="57" t="inlineStr">
-        <is>
-          <t>4. Boiler PLTU</t>
-        </is>
-      </c>
-      <c r="D235" s="57" t="inlineStr">
-        <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E235" s="57" t="inlineStr"/>
-      <c r="F235" s="58" t="n">
-        <v>1.8122687e-05</v>
-      </c>
-      <c r="G235" s="56" t="inlineStr">
-        <is>
-          <t>kg PO4--- eq</t>
-        </is>
-      </c>
-      <c r="H235" s="59" t="n">
-        <v>0.1877233383584696</v>
-      </c>
-      <c r="I235" s="59" t="n">
-        <v>0.9208738315475725</v>
-      </c>
-      <c r="J235" s="57" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
     </row>
@@ -19289,121 +19297,121 @@
       </c>
       <c r="B236" s="64" t="inlineStr">
         <is>
-          <t>POFP</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C236" s="65" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D236" s="65" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E236" s="65" t="inlineStr"/>
       <c r="F236" s="66" t="n">
+        <v>2.1783575e-05</v>
+      </c>
+      <c r="G236" s="64" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H236" s="67" t="n">
+        <v>0.2256445426874116</v>
+      </c>
+      <c r="I236" s="67" t="n">
+        <v>0.733150493189103</v>
+      </c>
+      <c r="J236" s="65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="30" customHeight="1">
+      <c r="A237" s="56" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B237" s="56" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C237" s="57" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="D237" s="57" t="inlineStr">
+        <is>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E237" s="57" t="inlineStr"/>
+      <c r="F237" s="58" t="n">
+        <v>1.8122687e-05</v>
+      </c>
+      <c r="G237" s="56" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H237" s="59" t="n">
+        <v>0.1877233383584696</v>
+      </c>
+      <c r="I237" s="59" t="n">
+        <v>0.9208738315475725</v>
+      </c>
+      <c r="J237" s="57" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="30" customHeight="1">
+      <c r="A238" s="64" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B238" s="64" t="inlineStr">
+        <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="C238" s="65" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="D238" s="65" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="E238" s="65" t="inlineStr"/>
+      <c r="F238" s="66" t="n">
         <v>1.0150836e-05</v>
       </c>
-      <c r="G236" s="64" t="inlineStr">
+      <c r="G238" s="64" t="inlineStr">
         <is>
           <t>kg C2H4 eq</t>
         </is>
       </c>
-      <c r="H236" s="67" t="n">
+      <c r="H238" s="67" t="n">
         <v>0.4952907824949865</v>
       </c>
-      <c r="I236" s="67" t="n">
+      <c r="I238" s="67" t="n">
         <v>0.4952907824949865</v>
       </c>
-      <c r="J236" s="65" t="inlineStr">
+      <c r="J238" s="65" t="inlineStr">
         <is>
           <t>126</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="30" customHeight="1">
-      <c r="A237" s="60" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B237" s="60" t="inlineStr">
-        <is>
-          <t>POFP</t>
-        </is>
-      </c>
-      <c r="C237" s="61" t="inlineStr">
-        <is>
-          <t>2. Coal Transport Export</t>
-        </is>
-      </c>
-      <c r="D237" s="61" t="inlineStr">
-        <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E237" s="61" t="inlineStr"/>
-      <c r="F237" s="62" t="n">
-        <v>6.0925296e-06</v>
-      </c>
-      <c r="G237" s="60" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H237" s="63" t="n">
-        <v>0.297273421909079</v>
-      </c>
-      <c r="I237" s="63" t="n">
-        <v>0.7925642044040655</v>
-      </c>
-      <c r="J237" s="61" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="30" customHeight="1">
-      <c r="A238" s="56" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B238" s="56" t="inlineStr">
-        <is>
-          <t>POFP</t>
-        </is>
-      </c>
-      <c r="C238" s="57" t="inlineStr">
-        <is>
-          <t>4. Boiler PLTU</t>
-        </is>
-      </c>
-      <c r="D238" s="57" t="inlineStr">
-        <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E238" s="57" t="inlineStr"/>
-      <c r="F238" s="58" t="n">
-        <v>2.6690009e-06</v>
-      </c>
-      <c r="G238" s="56" t="inlineStr">
-        <is>
-          <t>kg C2H4 eq</t>
-        </is>
-      </c>
-      <c r="H238" s="59" t="n">
-        <v>0.1302288347719167</v>
-      </c>
-      <c r="I238" s="59" t="n">
-        <v>0.9227930391759822</v>
-      </c>
-      <c r="J238" s="57" t="inlineStr">
-        <is>
-          <t>128</t>
         </is>
       </c>
     </row>
@@ -19415,37 +19423,37 @@
       </c>
       <c r="B239" s="60" t="inlineStr">
         <is>
-          <t>ABF</t>
+          <t>POFP</t>
         </is>
       </c>
       <c r="C239" s="61" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D239" s="61" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E239" s="61" t="inlineStr"/>
       <c r="F239" s="62" t="n">
-        <v>0.19624421</v>
+        <v>6.0925296e-06</v>
       </c>
       <c r="G239" s="60" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>kg C2H4 eq</t>
         </is>
       </c>
       <c r="H239" s="63" t="n">
-        <v>0.5106228028260794</v>
+        <v>0.297273421909079</v>
       </c>
       <c r="I239" s="63" t="n">
-        <v>0.5106228028260794</v>
+        <v>0.7925642044040655</v>
       </c>
       <c r="J239" s="61" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -19457,37 +19465,37 @@
       </c>
       <c r="B240" s="56" t="inlineStr">
         <is>
-          <t>ABF</t>
+          <t>POFP</t>
         </is>
       </c>
       <c r="C240" s="57" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D240" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E240" s="57" t="inlineStr"/>
       <c r="F240" s="58" t="n">
-        <v>0.119662</v>
+        <v>2.6690009e-06</v>
       </c>
       <c r="G240" s="56" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>kg C2H4 eq</t>
         </is>
       </c>
       <c r="H240" s="59" t="n">
-        <v>0.3113576998362108</v>
+        <v>0.1302288347719167</v>
       </c>
       <c r="I240" s="59" t="n">
-        <v>0.8219805026622902</v>
+        <v>0.9227930391759822</v>
       </c>
       <c r="J240" s="57" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -19499,37 +19507,37 @@
       </c>
       <c r="B241" s="60" t="inlineStr">
         <is>
-          <t>ABN</t>
+          <t>ABF</t>
         </is>
       </c>
       <c r="C241" s="61" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D241" s="61" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E241" s="61" t="inlineStr"/>
       <c r="F241" s="62" t="n">
-        <v>1.5848181e-08</v>
+        <v>0.19624421</v>
       </c>
       <c r="G241" s="60" t="inlineStr">
         <is>
-          <t>kg Sb eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H241" s="63" t="n">
-        <v>0.6201122794210921</v>
+        <v>0.5106228028260794</v>
       </c>
       <c r="I241" s="63" t="n">
-        <v>0.6201122794210921</v>
+        <v>0.5106228028260794</v>
       </c>
       <c r="J241" s="61" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -19541,37 +19549,37 @@
       </c>
       <c r="B242" s="56" t="inlineStr">
         <is>
-          <t>ABN</t>
+          <t>ABF</t>
         </is>
       </c>
       <c r="C242" s="57" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D242" s="57" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E242" s="57" t="inlineStr"/>
       <c r="F242" s="58" t="n">
-        <v>5.915427e-09</v>
+        <v>0.119662</v>
       </c>
       <c r="G242" s="56" t="inlineStr">
         <is>
-          <t>kg Sb eq</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="H242" s="59" t="n">
-        <v>0.2314605645101525</v>
+        <v>0.3113576998362108</v>
       </c>
       <c r="I242" s="59" t="n">
-        <v>0.8515728439312447</v>
+        <v>0.8219805026622902</v>
       </c>
       <c r="J242" s="57" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -19583,7 +19591,7 @@
       </c>
       <c r="B243" s="60" t="inlineStr">
         <is>
-          <t>ETP Terrestrial</t>
+          <t>ABN</t>
         </is>
       </c>
       <c r="C243" s="61" t="inlineStr">
@@ -19598,22 +19606,22 @@
       </c>
       <c r="E243" s="61" t="inlineStr"/>
       <c r="F243" s="62" t="n">
-        <v>0.025770467</v>
+        <v>1.5848181e-08</v>
       </c>
       <c r="G243" s="60" t="inlineStr">
         <is>
-          <t>kg 1,4-DCB</t>
+          <t>kg Sb eq</t>
         </is>
       </c>
       <c r="H243" s="63" t="n">
-        <v>0.6244143072071927</v>
+        <v>0.6201122794210921</v>
       </c>
       <c r="I243" s="63" t="n">
-        <v>0.6244143072071927</v>
+        <v>0.6201122794210921</v>
       </c>
       <c r="J243" s="61" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -19625,7 +19633,7 @@
       </c>
       <c r="B244" s="56" t="inlineStr">
         <is>
-          <t>ETP Terrestrial</t>
+          <t>ABN</t>
         </is>
       </c>
       <c r="C244" s="57" t="inlineStr">
@@ -19640,22 +19648,22 @@
       </c>
       <c r="E244" s="57" t="inlineStr"/>
       <c r="F244" s="58" t="n">
-        <v>0.0093493094</v>
+        <v>5.915427e-09</v>
       </c>
       <c r="G244" s="56" t="inlineStr">
         <is>
-          <t>kg 1,4-DCB</t>
+          <t>kg Sb eq</t>
         </is>
       </c>
       <c r="H244" s="59" t="n">
-        <v>0.2265322763404596</v>
+        <v>0.2314605645101525</v>
       </c>
       <c r="I244" s="59" t="n">
-        <v>0.8509465835476523</v>
+        <v>0.8515728439312447</v>
       </c>
       <c r="J244" s="57" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -19667,22 +19675,22 @@
       </c>
       <c r="B245" s="60" t="inlineStr">
         <is>
-          <t>ETP Freshwater</t>
+          <t>ETP Terrestrial</t>
         </is>
       </c>
       <c r="C245" s="61" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D245" s="61" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E245" s="61" t="inlineStr"/>
       <c r="F245" s="62" t="n">
-        <v>8.580679e-06</v>
+        <v>0.025770467</v>
       </c>
       <c r="G245" s="60" t="inlineStr">
         <is>
@@ -19690,14 +19698,14 @@
         </is>
       </c>
       <c r="H245" s="63" t="n">
-        <v>0.5203774730528871</v>
+        <v>0.6244143072071927</v>
       </c>
       <c r="I245" s="63" t="n">
-        <v>0.5203774730528871</v>
+        <v>0.6244143072071927</v>
       </c>
       <c r="J245" s="61" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -19709,22 +19717,22 @@
       </c>
       <c r="B246" s="56" t="inlineStr">
         <is>
-          <t>ETP Freshwater</t>
+          <t>ETP Terrestrial</t>
         </is>
       </c>
       <c r="C246" s="57" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D246" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E246" s="57" t="inlineStr"/>
       <c r="F246" s="58" t="n">
-        <v>5.0189531e-06</v>
+        <v>0.0093493094</v>
       </c>
       <c r="G246" s="56" t="inlineStr">
         <is>
@@ -19732,14 +19740,14 @@
         </is>
       </c>
       <c r="H246" s="59" t="n">
-        <v>0.3043756946914054</v>
+        <v>0.2265322763404596</v>
       </c>
       <c r="I246" s="59" t="n">
-        <v>0.8247531677442925</v>
+        <v>0.8509465835476523</v>
       </c>
       <c r="J246" s="57" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -19751,22 +19759,22 @@
       </c>
       <c r="B247" s="60" t="inlineStr">
         <is>
-          <t>ETP Marine</t>
+          <t>ETP Freshwater</t>
         </is>
       </c>
       <c r="C247" s="61" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D247" s="61" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E247" s="61" t="inlineStr"/>
       <c r="F247" s="62" t="n">
-        <v>2.4636066e-05</v>
+        <v>8.580679e-06</v>
       </c>
       <c r="G247" s="60" t="inlineStr">
         <is>
@@ -19774,14 +19782,14 @@
         </is>
       </c>
       <c r="H247" s="63" t="n">
-        <v>0.4925147790022776</v>
+        <v>0.5203774730528871</v>
       </c>
       <c r="I247" s="63" t="n">
-        <v>0.4925147790022776</v>
+        <v>0.5203774730528871</v>
       </c>
       <c r="J247" s="61" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -19793,22 +19801,22 @@
       </c>
       <c r="B248" s="56" t="inlineStr">
         <is>
-          <t>ETP Marine</t>
+          <t>ETP Freshwater</t>
         </is>
       </c>
       <c r="C248" s="57" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D248" s="57" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E248" s="57" t="inlineStr"/>
       <c r="F248" s="58" t="n">
-        <v>1.731507e-05</v>
+        <v>5.0189531e-06</v>
       </c>
       <c r="G248" s="56" t="inlineStr">
         <is>
@@ -19816,14 +19824,14 @@
         </is>
       </c>
       <c r="H248" s="59" t="n">
-        <v>0.3461562359209042</v>
+        <v>0.3043756946914054</v>
       </c>
       <c r="I248" s="59" t="n">
-        <v>0.8386710149231817</v>
+        <v>0.8247531677442925</v>
       </c>
       <c r="J248" s="57" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19843,7 @@
       </c>
       <c r="B249" s="60" t="inlineStr">
         <is>
-          <t>HTC</t>
+          <t>ETP Marine</t>
         </is>
       </c>
       <c r="C249" s="61" t="inlineStr">
@@ -19850,7 +19858,7 @@
       </c>
       <c r="E249" s="61" t="inlineStr"/>
       <c r="F249" s="62" t="n">
-        <v>0.00014550155</v>
+        <v>2.4636066e-05</v>
       </c>
       <c r="G249" s="60" t="inlineStr">
         <is>
@@ -19858,14 +19866,14 @@
         </is>
       </c>
       <c r="H249" s="63" t="n">
-        <v>0.445330072225647</v>
+        <v>0.4925147790022776</v>
       </c>
       <c r="I249" s="63" t="n">
-        <v>0.445330072225647</v>
+        <v>0.4925147790022776</v>
       </c>
       <c r="J249" s="61" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>261</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19885,7 @@
       </c>
       <c r="B250" s="56" t="inlineStr">
         <is>
-          <t>HTC</t>
+          <t>ETP Marine</t>
         </is>
       </c>
       <c r="C250" s="57" t="inlineStr">
@@ -19892,7 +19900,7 @@
       </c>
       <c r="E250" s="57" t="inlineStr"/>
       <c r="F250" s="58" t="n">
-        <v>0.00012852226</v>
+        <v>1.731507e-05</v>
       </c>
       <c r="G250" s="56" t="inlineStr">
         <is>
@@ -19900,14 +19908,14 @@
         </is>
       </c>
       <c r="H250" s="59" t="n">
-        <v>0.3933623203904245</v>
+        <v>0.3461562359209042</v>
       </c>
       <c r="I250" s="59" t="n">
-        <v>0.8386923926160714</v>
+        <v>0.8386710149231817</v>
       </c>
       <c r="J250" s="57" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>262</t>
         </is>
       </c>
     </row>
@@ -19919,22 +19927,22 @@
       </c>
       <c r="B251" s="60" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>HTC</t>
         </is>
       </c>
       <c r="C251" s="61" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D251" s="61" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E251" s="61" t="inlineStr"/>
       <c r="F251" s="62" t="n">
-        <v>0.0029773508</v>
+        <v>0.00014550155</v>
       </c>
       <c r="G251" s="60" t="inlineStr">
         <is>
@@ -19942,14 +19950,14 @@
         </is>
       </c>
       <c r="H251" s="63" t="n">
-        <v>0.6770073398094784</v>
+        <v>0.445330072225647</v>
       </c>
       <c r="I251" s="63" t="n">
-        <v>0.6770073398094784</v>
+        <v>0.445330072225647</v>
       </c>
       <c r="J251" s="61" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -19961,12 +19969,12 @@
       </c>
       <c r="B252" s="56" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>HTC</t>
         </is>
       </c>
       <c r="C252" s="57" t="inlineStr">
         <is>
-          <t>3. Coal Mill</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D252" s="57" t="inlineStr">
@@ -19976,106 +19984,106 @@
       </c>
       <c r="E252" s="57" t="inlineStr"/>
       <c r="F252" s="58" t="n">
+        <v>0.00012852226</v>
+      </c>
+      <c r="G252" s="56" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H252" s="59" t="n">
+        <v>0.3933623203904245</v>
+      </c>
+      <c r="I252" s="59" t="n">
+        <v>0.8386923926160714</v>
+      </c>
+      <c r="J252" s="57" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="30" customHeight="1">
+      <c r="A253" s="60" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B253" s="60" t="inlineStr">
+        <is>
+          <t>HTN</t>
+        </is>
+      </c>
+      <c r="C253" s="61" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="D253" s="61" t="inlineStr">
+        <is>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E253" s="61" t="inlineStr"/>
+      <c r="F253" s="62" t="n">
+        <v>0.0029773508</v>
+      </c>
+      <c r="G253" s="60" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="H253" s="63" t="n">
+        <v>0.6770073398094784</v>
+      </c>
+      <c r="I253" s="63" t="n">
+        <v>0.6770073398094784</v>
+      </c>
+      <c r="J253" s="61" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="56" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B254" s="56" t="inlineStr">
+        <is>
+          <t>HTN</t>
+        </is>
+      </c>
+      <c r="C254" s="57" t="inlineStr">
+        <is>
+          <t>3. Coal Mill</t>
+        </is>
+      </c>
+      <c r="D254" s="57" t="inlineStr">
+        <is>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E254" s="57" t="inlineStr"/>
+      <c r="F254" s="58" t="n">
         <v>0.00071861733</v>
       </c>
-      <c r="G252" s="56" t="inlineStr">
+      <c r="G254" s="56" t="inlineStr">
         <is>
           <t>kg 1,4-DCB</t>
         </is>
       </c>
-      <c r="H252" s="59" t="n">
+      <c r="H254" s="59" t="n">
         <v>0.1634033876439048</v>
       </c>
-      <c r="I252" s="59" t="n">
+      <c r="I254" s="59" t="n">
         <v>0.8404107274533832</v>
       </c>
-      <c r="J252" s="57" t="inlineStr">
+      <c r="J254" s="57" t="inlineStr">
         <is>
           <t>315</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="30" customHeight="1">
-      <c r="A253" s="56" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B253" s="56" t="inlineStr">
-        <is>
-          <t>WSF</t>
-        </is>
-      </c>
-      <c r="C253" s="57" t="inlineStr">
-        <is>
-          <t>5. Turbine PLTU</t>
-        </is>
-      </c>
-      <c r="D253" s="57" t="inlineStr">
-        <is>
-          <t>5. Turbine PLTU</t>
-        </is>
-      </c>
-      <c r="E253" s="57" t="inlineStr"/>
-      <c r="F253" s="58" t="n">
-        <v>-0.13377858</v>
-      </c>
-      <c r="G253" s="56" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="H253" s="59" t="n">
-        <v>-2.140863358961928</v>
-      </c>
-      <c r="I253" s="59" t="n">
-        <v>2.140863358961928</v>
-      </c>
-      <c r="J253" s="57" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="64" t="inlineStr">
-        <is>
-          <t>PROC DOWN LMO</t>
-        </is>
-      </c>
-      <c r="B254" s="64" t="inlineStr">
-        <is>
-          <t>LUC</t>
-        </is>
-      </c>
-      <c r="C254" s="65" t="inlineStr">
-        <is>
-          <t>2. Coal Transport Export</t>
-        </is>
-      </c>
-      <c r="D254" s="65" t="inlineStr">
-        <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
-        </is>
-      </c>
-      <c r="E254" s="65" t="inlineStr"/>
-      <c r="F254" s="66" t="n">
-        <v>0.00013678168</v>
-      </c>
-      <c r="G254" s="64" t="inlineStr">
-        <is>
-          <t>m2a crop eq</t>
-        </is>
-      </c>
-      <c r="H254" s="67" t="n">
-        <v>0.5940359058547604</v>
-      </c>
-      <c r="I254" s="67" t="n">
-        <v>0.5940359058547604</v>
-      </c>
-      <c r="J254" s="65" t="inlineStr">
-        <is>
-          <t>342</t>
         </is>
       </c>
     </row>
@@ -20087,37 +20095,37 @@
       </c>
       <c r="B255" s="56" t="inlineStr">
         <is>
-          <t>LUC</t>
+          <t>WSF</t>
         </is>
       </c>
       <c r="C255" s="57" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>5. Turbine PLTU</t>
         </is>
       </c>
       <c r="D255" s="57" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>5. Turbine PLTU</t>
         </is>
       </c>
       <c r="E255" s="57" t="inlineStr"/>
       <c r="F255" s="58" t="n">
-        <v>5.6436149e-05</v>
+        <v>-0.13377858</v>
       </c>
       <c r="G255" s="56" t="inlineStr">
         <is>
-          <t>m2a crop eq</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="H255" s="59" t="n">
-        <v>0.2450993356286399</v>
+        <v>-2.140863358961928</v>
       </c>
       <c r="I255" s="59" t="n">
-        <v>0.8391352414834004</v>
+        <v>2.140863358961928</v>
       </c>
       <c r="J255" s="57" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -20129,37 +20137,37 @@
       </c>
       <c r="B256" s="64" t="inlineStr">
         <is>
-          <t>CEN</t>
+          <t>LUC</t>
         </is>
       </c>
       <c r="C256" s="65" t="inlineStr">
         <is>
-          <t>4. Boiler PLTU</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D256" s="65" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E256" s="65" t="inlineStr"/>
       <c r="F256" s="66" t="n">
-        <v>0.22086487749715</v>
+        <v>0.00013678168</v>
       </c>
       <c r="G256" s="64" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>m2a crop eq</t>
         </is>
       </c>
       <c r="H256" s="67" t="n">
-        <v>0.520170133905293</v>
+        <v>0.5940359058547604</v>
       </c>
       <c r="I256" s="67" t="n">
-        <v>0.520170133905293</v>
+        <v>0.5940359058547604</v>
       </c>
       <c r="J256" s="65" t="inlineStr">
         <is>
-          <t>396, 423, 451</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -20171,37 +20179,37 @@
       </c>
       <c r="B257" s="56" t="inlineStr">
         <is>
-          <t>CEN</t>
+          <t>LUC</t>
         </is>
       </c>
       <c r="C257" s="57" t="inlineStr">
         <is>
-          <t>2. Coal Transport Export</t>
+          <t>4. Boiler PLTU</t>
         </is>
       </c>
       <c r="D257" s="57" t="inlineStr">
         <is>
-          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
         </is>
       </c>
       <c r="E257" s="57" t="inlineStr"/>
       <c r="F257" s="58" t="n">
-        <v>0.127938595038</v>
+        <v>5.6436149e-05</v>
       </c>
       <c r="G257" s="56" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>m2a crop eq</t>
         </is>
       </c>
       <c r="H257" s="59" t="n">
-        <v>0.3013147081904422</v>
+        <v>0.2450993356286399</v>
       </c>
       <c r="I257" s="59" t="n">
-        <v>0.8214848420957352</v>
+        <v>0.8391352414834004</v>
       </c>
       <c r="J257" s="57" t="inlineStr">
         <is>
-          <t>397, 424, 450</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20221,7 @@
       </c>
       <c r="B258" s="64" t="inlineStr">
         <is>
-          <t>CED</t>
+          <t>CEN</t>
         </is>
       </c>
       <c r="C258" s="65" t="inlineStr">
@@ -20228,7 +20236,7 @@
       </c>
       <c r="E258" s="65" t="inlineStr"/>
       <c r="F258" s="66" t="n">
-        <v>0.007912694160000001</v>
+        <v>0.22086487749715</v>
       </c>
       <c r="G258" s="64" t="inlineStr">
         <is>
@@ -20236,14 +20244,14 @@
         </is>
       </c>
       <c r="H258" s="67" t="n">
-        <v>0.7254432151709567</v>
+        <v>0.520170133905293</v>
       </c>
       <c r="I258" s="67" t="n">
-        <v>0.7254432151709567</v>
+        <v>0.520170133905293</v>
       </c>
       <c r="J258" s="65" t="inlineStr">
         <is>
-          <t>478, 504, 531</t>
+          <t>396, 423, 451</t>
         </is>
       </c>
     </row>
@@ -20255,42 +20263,126 @@
       </c>
       <c r="B259" s="56" t="inlineStr">
         <is>
-          <t>CED</t>
+          <t>CEN</t>
         </is>
       </c>
       <c r="C259" s="57" t="inlineStr">
         <is>
-          <t>3. Coal Mill</t>
+          <t>2. Coal Transport Export</t>
         </is>
       </c>
       <c r="D259" s="57" t="inlineStr">
         <is>
-          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+          <t>Transport, freight, sea, bulk carrier for dry goods {GLO}| market for transport, freight, sea, bulk carrier for dry goods | Cut-off, S</t>
         </is>
       </c>
       <c r="E259" s="57" t="inlineStr"/>
       <c r="F259" s="58" t="n">
+        <v>0.127938595038</v>
+      </c>
+      <c r="G259" s="56" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H259" s="59" t="n">
+        <v>0.3013147081904422</v>
+      </c>
+      <c r="I259" s="59" t="n">
+        <v>0.8214848420957352</v>
+      </c>
+      <c r="J259" s="57" t="inlineStr">
+        <is>
+          <t>397, 424, 450</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="64" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B260" s="64" t="inlineStr">
+        <is>
+          <t>CED</t>
+        </is>
+      </c>
+      <c r="C260" s="65" t="inlineStr">
+        <is>
+          <t>4. Boiler PLTU</t>
+        </is>
+      </c>
+      <c r="D260" s="65" t="inlineStr">
+        <is>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E260" s="65" t="inlineStr"/>
+      <c r="F260" s="66" t="n">
+        <v>0.007912694160000001</v>
+      </c>
+      <c r="G260" s="64" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="H260" s="67" t="n">
+        <v>0.7254432151709567</v>
+      </c>
+      <c r="I260" s="67" t="n">
+        <v>0.7254432151709567</v>
+      </c>
+      <c r="J260" s="65" t="inlineStr">
+        <is>
+          <t>478, 504, 531</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="56" t="inlineStr">
+        <is>
+          <t>PROC DOWN LMO</t>
+        </is>
+      </c>
+      <c r="B261" s="56" t="inlineStr">
+        <is>
+          <t>CED</t>
+        </is>
+      </c>
+      <c r="C261" s="57" t="inlineStr">
+        <is>
+          <t>3. Coal Mill</t>
+        </is>
+      </c>
+      <c r="D261" s="57" t="inlineStr">
+        <is>
+          <t>Electricity, high voltage {ID}| production mix | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="E261" s="57" t="inlineStr"/>
+      <c r="F261" s="58" t="n">
         <v>0.001909818399</v>
       </c>
-      <c r="G259" s="56" t="inlineStr">
+      <c r="G261" s="56" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
       </c>
-      <c r="H259" s="59" t="n">
+      <c r="H261" s="59" t="n">
         <v>0.1750939404137426</v>
       </c>
-      <c r="I259" s="59" t="n">
+      <c r="I261" s="59" t="n">
         <v>0.9005371555846993</v>
       </c>
-      <c r="J259" s="57" t="inlineStr">
+      <c r="J261" s="57" t="inlineStr">
         <is>
           <t>478, 504, 531</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J259"/>
+  <autoFilter ref="A5:J261"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A3:J3"/>
